--- a/research/traditional_assets/database/data/malta/malta_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07794310438723719</v>
+        <v>0.07769955352188186</v>
       </c>
       <c r="C2">
-        <v>1322.855979673634</v>
+        <v>1312.217449921833</v>
       </c>
       <c r="D2">
-        <v>1178.555979673635</v>
+        <v>1181.150649921833</v>
       </c>
       <c r="E2">
-        <v>-3.22</v>
+        <v>10.0132</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.2332</v>
       </c>
       <c r="G2">
         <v>144.3</v>
@@ -1451,28 +1451,28 @@
         <v>203.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.66562996</v>
       </c>
       <c r="N2">
-        <v>203.1</v>
+        <v>202.43437004</v>
       </c>
       <c r="O2">
-        <v>71.08499999999999</v>
+        <v>70.85202951399999</v>
       </c>
       <c r="P2">
-        <v>132.015</v>
+        <v>131.582340526</v>
       </c>
       <c r="Q2">
-        <v>155.415</v>
+        <v>154.982340526</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07794310438723719</v>
+        <v>0.07815414497159784</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5925775274612076</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>305.1244868845748</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07769955352188186</v>
+        <v>0.07745600265652652</v>
       </c>
       <c r="C3">
-        <v>1312.217449921833</v>
+        <v>1301.590370059825</v>
       </c>
       <c r="D3">
-        <v>1181.150649921833</v>
+        <v>1183.756770059825</v>
       </c>
       <c r="E3">
-        <v>10.0132</v>
+        <v>23.2464</v>
       </c>
       <c r="F3">
-        <v>13.2332</v>
+        <v>26.4664</v>
       </c>
       <c r="G3">
         <v>144.3</v>
@@ -1533,28 +1533,28 @@
         <v>203.1</v>
       </c>
       <c r="M3">
-        <v>0.66562996</v>
+        <v>1.33125992</v>
       </c>
       <c r="N3">
-        <v>202.43437004</v>
+        <v>201.76874008</v>
       </c>
       <c r="O3">
-        <v>70.85202951399999</v>
+        <v>70.619059028</v>
       </c>
       <c r="P3">
-        <v>131.582340526</v>
+        <v>131.149681052</v>
       </c>
       <c r="Q3">
-        <v>154.982340526</v>
+        <v>154.549681052</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07815414497159784</v>
+        <v>0.07836949250665973</v>
       </c>
       <c r="T3">
-        <v>0.5925775274612076</v>
+        <v>0.5965216931927966</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>305.1244868845748</v>
+        <v>152.5622434422874</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07745600265652652</v>
+        <v>0.07721245179117119</v>
       </c>
       <c r="C4">
-        <v>1301.590370059825</v>
+        <v>1290.974816045169</v>
       </c>
       <c r="D4">
-        <v>1183.756770059825</v>
+        <v>1186.374416045169</v>
       </c>
       <c r="E4">
-        <v>23.2464</v>
+        <v>36.4796</v>
       </c>
       <c r="F4">
-        <v>26.4664</v>
+        <v>39.6996</v>
       </c>
       <c r="G4">
         <v>144.3</v>
@@ -1615,28 +1615,28 @@
         <v>203.1</v>
       </c>
       <c r="M4">
-        <v>1.33125992</v>
+        <v>1.99688988</v>
       </c>
       <c r="N4">
-        <v>201.76874008</v>
+        <v>201.10311012</v>
       </c>
       <c r="O4">
-        <v>70.619059028</v>
+        <v>70.386088542</v>
       </c>
       <c r="P4">
-        <v>131.149681052</v>
+        <v>130.717021578</v>
       </c>
       <c r="Q4">
-        <v>154.549681052</v>
+        <v>154.117021578</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07836949250665973</v>
+        <v>0.07858928019708369</v>
       </c>
       <c r="T4">
-        <v>0.5965216931927966</v>
+        <v>0.6005471819291605</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>152.5622434422874</v>
+        <v>101.7081622948583</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07721245179117119</v>
+        <v>0.07696890092581586</v>
       </c>
       <c r="C5">
-        <v>1290.974816045169</v>
+        <v>1280.370864508772</v>
       </c>
       <c r="D5">
-        <v>1186.374416045169</v>
+        <v>1189.003664508772</v>
       </c>
       <c r="E5">
-        <v>36.4796</v>
+        <v>49.7128</v>
       </c>
       <c r="F5">
-        <v>39.6996</v>
+        <v>52.9328</v>
       </c>
       <c r="G5">
         <v>144.3</v>
@@ -1697,28 +1697,28 @@
         <v>203.1</v>
       </c>
       <c r="M5">
-        <v>1.99688988</v>
+        <v>2.66251984</v>
       </c>
       <c r="N5">
-        <v>201.10311012</v>
+        <v>200.43748016</v>
       </c>
       <c r="O5">
-        <v>70.386088542</v>
+        <v>70.153118056</v>
       </c>
       <c r="P5">
-        <v>130.717021578</v>
+        <v>130.284362104</v>
       </c>
       <c r="Q5">
-        <v>154.117021578</v>
+        <v>153.684362104</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07858928019708369</v>
+        <v>0.07881364679772486</v>
       </c>
       <c r="T5">
-        <v>0.6005471819291605</v>
+        <v>0.6046565350141988</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>101.7081622948583</v>
+        <v>76.28112172114369</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07696890092581586</v>
+        <v>0.07672535006046052</v>
       </c>
       <c r="C6">
-        <v>1280.370864508772</v>
+        <v>1269.778592762372</v>
       </c>
       <c r="D6">
-        <v>1189.003664508772</v>
+        <v>1191.644592762372</v>
       </c>
       <c r="E6">
-        <v>49.7128</v>
+        <v>62.946</v>
       </c>
       <c r="F6">
-        <v>52.9328</v>
+        <v>66.166</v>
       </c>
       <c r="G6">
         <v>144.3</v>
@@ -1779,28 +1779,28 @@
         <v>203.1</v>
       </c>
       <c r="M6">
-        <v>2.66251984</v>
+        <v>3.3281498</v>
       </c>
       <c r="N6">
-        <v>200.43748016</v>
+        <v>199.7718502</v>
       </c>
       <c r="O6">
-        <v>70.153118056</v>
+        <v>69.92014757</v>
       </c>
       <c r="P6">
-        <v>130.284362104</v>
+        <v>129.85170263</v>
       </c>
       <c r="Q6">
-        <v>153.684362104</v>
+        <v>153.25170263</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07881364679772486</v>
+        <v>0.07904273690574792</v>
       </c>
       <c r="T6">
-        <v>0.6046565350141988</v>
+        <v>0.6088524007957642</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>76.28112172114369</v>
+        <v>61.02489737691494</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07672535006046052</v>
+        <v>0.0764817991951052</v>
       </c>
       <c r="C7">
-        <v>1269.778592762372</v>
+        <v>1259.198078806111</v>
       </c>
       <c r="D7">
-        <v>1191.644592762372</v>
+        <v>1194.297278806111</v>
       </c>
       <c r="E7">
-        <v>62.946</v>
+        <v>76.17920000000001</v>
       </c>
       <c r="F7">
-        <v>66.166</v>
+        <v>79.39920000000001</v>
       </c>
       <c r="G7">
         <v>144.3</v>
@@ -1861,28 +1861,28 @@
         <v>203.1</v>
       </c>
       <c r="M7">
-        <v>3.3281498</v>
+        <v>3.99377976</v>
       </c>
       <c r="N7">
-        <v>199.7718502</v>
+        <v>199.10622024</v>
       </c>
       <c r="O7">
-        <v>69.92014757</v>
+        <v>69.687177084</v>
       </c>
       <c r="P7">
-        <v>129.85170263</v>
+        <v>129.419043156</v>
       </c>
       <c r="Q7">
-        <v>153.25170263</v>
+        <v>152.819043156</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07904273690574792</v>
+        <v>0.07927670127138851</v>
       </c>
       <c r="T7">
-        <v>0.6088524007957642</v>
+        <v>0.6131375403173629</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>61.02489737691494</v>
+        <v>50.85408114742912</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0764817991951052</v>
+        <v>0.07623824832974987</v>
       </c>
       <c r="C8">
-        <v>1259.198078806111</v>
+        <v>1248.629401336215</v>
       </c>
       <c r="D8">
-        <v>1194.297278806111</v>
+        <v>1196.961801336215</v>
       </c>
       <c r="E8">
-        <v>76.17919999999999</v>
+        <v>89.41239999999999</v>
       </c>
       <c r="F8">
-        <v>79.39919999999999</v>
+        <v>92.63239999999999</v>
       </c>
       <c r="G8">
         <v>144.3</v>
@@ -1943,28 +1943,28 @@
         <v>203.1</v>
       </c>
       <c r="M8">
-        <v>3.993779759999999</v>
+        <v>4.659409719999999</v>
       </c>
       <c r="N8">
-        <v>199.10622024</v>
+        <v>198.44059028</v>
       </c>
       <c r="O8">
-        <v>69.687177084</v>
+        <v>69.45420659799998</v>
       </c>
       <c r="P8">
-        <v>129.419043156</v>
+        <v>128.986383682</v>
       </c>
       <c r="Q8">
-        <v>152.819043156</v>
+        <v>152.386383682</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07927670127138851</v>
+        <v>0.0795156971287633</v>
       </c>
       <c r="T8">
-        <v>0.6131375403173629</v>
+        <v>0.6175148333770604</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.85408114742913</v>
+        <v>43.58921241208211</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07623824832974987</v>
+        <v>0.07599469746439455</v>
       </c>
       <c r="C9">
-        <v>1248.629401336215</v>
+        <v>1238.072639752781</v>
       </c>
       <c r="D9">
-        <v>1196.961801336215</v>
+        <v>1199.638239752781</v>
       </c>
       <c r="E9">
-        <v>89.41240000000001</v>
+        <v>102.6456</v>
       </c>
       <c r="F9">
-        <v>92.6324</v>
+        <v>105.8656</v>
       </c>
       <c r="G9">
         <v>144.3</v>
@@ -2025,28 +2025,28 @@
         <v>203.1</v>
       </c>
       <c r="M9">
-        <v>4.65940972</v>
+        <v>5.32503968</v>
       </c>
       <c r="N9">
-        <v>198.44059028</v>
+        <v>197.77496032</v>
       </c>
       <c r="O9">
-        <v>69.45420659799998</v>
+        <v>69.22123611199999</v>
       </c>
       <c r="P9">
-        <v>128.986383682</v>
+        <v>128.553724208</v>
       </c>
       <c r="Q9">
-        <v>152.386383682</v>
+        <v>151.953724208</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0795156971287633</v>
+        <v>0.07975988854825494</v>
       </c>
       <c r="T9">
-        <v>0.6175148333770604</v>
+        <v>0.621987284981534</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.5892124120821</v>
+        <v>38.14056086057184</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07599469746439455</v>
+        <v>0.07575114659903921</v>
       </c>
       <c r="C10">
-        <v>1238.072639752781</v>
+        <v>1227.527874167657</v>
       </c>
       <c r="D10">
-        <v>1199.638239752781</v>
+        <v>1202.326674167657</v>
       </c>
       <c r="E10">
-        <v>102.6456</v>
+        <v>115.8788</v>
       </c>
       <c r="F10">
-        <v>105.8656</v>
+        <v>119.0988</v>
       </c>
       <c r="G10">
         <v>144.3</v>
@@ -2107,28 +2107,28 @@
         <v>203.1</v>
       </c>
       <c r="M10">
-        <v>5.32503968</v>
+        <v>5.990669639999999</v>
       </c>
       <c r="N10">
-        <v>197.77496032</v>
+        <v>197.10933036</v>
       </c>
       <c r="O10">
-        <v>69.22123611199999</v>
+        <v>68.988265626</v>
       </c>
       <c r="P10">
-        <v>128.553724208</v>
+        <v>128.121064734</v>
       </c>
       <c r="Q10">
-        <v>151.953724208</v>
+        <v>151.521064734</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07975988854825494</v>
+        <v>0.080009446812131</v>
       </c>
       <c r="T10">
-        <v>0.621987284981534</v>
+        <v>0.6265580322256664</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.14056086057184</v>
+        <v>33.90272076495275</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07575114659903921</v>
+        <v>0.07550759573368387</v>
       </c>
       <c r="C11">
-        <v>1227.527874167657</v>
+        <v>1216.995185412439</v>
       </c>
       <c r="D11">
-        <v>1202.326674167657</v>
+        <v>1205.027185412439</v>
       </c>
       <c r="E11">
-        <v>115.8788</v>
+        <v>129.112</v>
       </c>
       <c r="F11">
-        <v>119.0988</v>
+        <v>132.332</v>
       </c>
       <c r="G11">
         <v>144.3</v>
@@ -2189,28 +2189,28 @@
         <v>203.1</v>
       </c>
       <c r="M11">
-        <v>5.990669639999999</v>
+        <v>6.6562996</v>
       </c>
       <c r="N11">
-        <v>197.10933036</v>
+        <v>196.4437004</v>
       </c>
       <c r="O11">
-        <v>68.988265626</v>
+        <v>68.75529513999999</v>
       </c>
       <c r="P11">
-        <v>128.121064734</v>
+        <v>127.68840526</v>
       </c>
       <c r="Q11">
-        <v>151.521064734</v>
+        <v>151.08840526</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.080009446812131</v>
+        <v>0.08026455081520431</v>
       </c>
       <c r="T11">
-        <v>0.6265580322256664</v>
+        <v>0.6312303516307796</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.90272076495275</v>
+        <v>30.51244868845747</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07550759573368387</v>
+        <v>0.07526404486832855</v>
       </c>
       <c r="C12">
-        <v>1216.995185412439</v>
+        <v>1206.474655046575</v>
       </c>
       <c r="D12">
-        <v>1205.027185412439</v>
+        <v>1207.739855046575</v>
       </c>
       <c r="E12">
-        <v>129.112</v>
+        <v>142.3452</v>
       </c>
       <c r="F12">
-        <v>132.332</v>
+        <v>145.5652</v>
       </c>
       <c r="G12">
         <v>144.3</v>
@@ -2271,28 +2271,28 @@
         <v>203.1</v>
       </c>
       <c r="M12">
-        <v>6.6562996</v>
+        <v>7.32192956</v>
       </c>
       <c r="N12">
-        <v>196.4437004</v>
+        <v>195.77807044</v>
       </c>
       <c r="O12">
-        <v>68.75529513999999</v>
+        <v>68.52232465399999</v>
       </c>
       <c r="P12">
-        <v>127.68840526</v>
+        <v>127.255745786</v>
       </c>
       <c r="Q12">
-        <v>151.08840526</v>
+        <v>150.655745786</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08026455081520431</v>
+        <v>0.08052538749250399</v>
       </c>
       <c r="T12">
-        <v>0.6312303516307796</v>
+        <v>0.6360076669775806</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.51244868845747</v>
+        <v>27.73858971677952</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07526404486832855</v>
+        <v>0.07502049400297323</v>
       </c>
       <c r="C13">
-        <v>1206.474655046575</v>
+        <v>1195.966365365568</v>
       </c>
       <c r="D13">
-        <v>1207.739855046575</v>
+        <v>1210.464765365568</v>
       </c>
       <c r="E13">
-        <v>142.3452</v>
+        <v>155.5784</v>
       </c>
       <c r="F13">
-        <v>145.5652</v>
+        <v>158.7984</v>
       </c>
       <c r="G13">
         <v>144.3</v>
@@ -2353,28 +2353,28 @@
         <v>203.1</v>
       </c>
       <c r="M13">
-        <v>7.32192956</v>
+        <v>7.987559519999999</v>
       </c>
       <c r="N13">
-        <v>195.77807044</v>
+        <v>195.11244048</v>
       </c>
       <c r="O13">
-        <v>68.52232465399999</v>
+        <v>68.289354168</v>
       </c>
       <c r="P13">
-        <v>127.255745786</v>
+        <v>126.823086312</v>
       </c>
       <c r="Q13">
-        <v>150.655745786</v>
+        <v>150.223086312</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08052538749250399</v>
+        <v>0.08079215227610594</v>
       </c>
       <c r="T13">
-        <v>0.6360076669775806</v>
+        <v>0.6408935576731726</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.73858971677952</v>
+        <v>25.42704057371456</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07502049400297323</v>
+        <v>0.07477694313761789</v>
       </c>
       <c r="C14">
-        <v>1195.966365365568</v>
+        <v>1185.470399409307</v>
       </c>
       <c r="D14">
-        <v>1210.464765365568</v>
+        <v>1213.201999409307</v>
       </c>
       <c r="E14">
-        <v>155.5784</v>
+        <v>168.8116</v>
       </c>
       <c r="F14">
-        <v>158.7984</v>
+        <v>172.0316</v>
       </c>
       <c r="G14">
         <v>144.3</v>
@@ -2435,28 +2435,28 @@
         <v>203.1</v>
       </c>
       <c r="M14">
-        <v>7.987559519999999</v>
+        <v>8.65318948</v>
       </c>
       <c r="N14">
-        <v>195.11244048</v>
+        <v>194.44681052</v>
       </c>
       <c r="O14">
-        <v>68.289354168</v>
+        <v>68.05638368199999</v>
       </c>
       <c r="P14">
-        <v>126.823086312</v>
+        <v>126.390426838</v>
       </c>
       <c r="Q14">
-        <v>150.223086312</v>
+        <v>149.790426838</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08079215227610594</v>
+        <v>0.08106504958346884</v>
       </c>
       <c r="T14">
-        <v>0.6408935576731726</v>
+        <v>0.6458917676950999</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.42704057371456</v>
+        <v>23.47111437573652</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07477694313761789</v>
+        <v>0.07453339227226258</v>
       </c>
       <c r="C15">
-        <v>1185.470399409307</v>
+        <v>1174.986840970496</v>
       </c>
       <c r="D15">
-        <v>1213.201999409307</v>
+        <v>1215.951640970496</v>
       </c>
       <c r="E15">
-        <v>168.8116</v>
+        <v>182.0448</v>
       </c>
       <c r="F15">
-        <v>172.0316</v>
+        <v>185.2648</v>
       </c>
       <c r="G15">
         <v>144.3</v>
@@ -2517,28 +2517,28 @@
         <v>203.1</v>
       </c>
       <c r="M15">
-        <v>8.65318948</v>
+        <v>9.31881944</v>
       </c>
       <c r="N15">
-        <v>194.44681052</v>
+        <v>193.78118056</v>
       </c>
       <c r="O15">
-        <v>68.05638368199999</v>
+        <v>67.82341319599999</v>
       </c>
       <c r="P15">
-        <v>126.390426838</v>
+        <v>125.957767364</v>
       </c>
       <c r="Q15">
-        <v>149.790426838</v>
+        <v>149.357767364</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08106504958346884</v>
+        <v>0.0813442933398402</v>
       </c>
       <c r="T15">
-        <v>0.6458917676950999</v>
+        <v>0.6510062151593978</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.47111437573652</v>
+        <v>21.79460620604105</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07453339227226258</v>
+        <v>0.07428984140690724</v>
       </c>
       <c r="C16">
-        <v>1174.986840970496</v>
+        <v>1164.515774603209</v>
       </c>
       <c r="D16">
-        <v>1215.951640970496</v>
+        <v>1218.713774603209</v>
       </c>
       <c r="E16">
-        <v>182.0448</v>
+        <v>195.278</v>
       </c>
       <c r="F16">
-        <v>185.2648</v>
+        <v>198.498</v>
       </c>
       <c r="G16">
         <v>144.3</v>
@@ -2599,28 +2599,28 @@
         <v>203.1</v>
       </c>
       <c r="M16">
-        <v>9.31881944</v>
+        <v>9.984449400000001</v>
       </c>
       <c r="N16">
-        <v>193.78118056</v>
+        <v>193.1155506</v>
       </c>
       <c r="O16">
-        <v>67.82341319599999</v>
+        <v>67.59044270999999</v>
       </c>
       <c r="P16">
-        <v>125.957767364</v>
+        <v>125.52510789</v>
       </c>
       <c r="Q16">
-        <v>149.357767364</v>
+        <v>148.92510789</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0813442933398402</v>
+        <v>0.08163010753753792</v>
       </c>
       <c r="T16">
-        <v>0.6510062151593978</v>
+        <v>0.6562410025640321</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.79460620604105</v>
+        <v>20.34163245897165</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07428984140690724</v>
+        <v>0.07404629054155192</v>
       </c>
       <c r="C17">
-        <v>1164.515774603209</v>
+        <v>1154.057285631554</v>
       </c>
       <c r="D17">
-        <v>1218.713774603209</v>
+        <v>1221.488485631554</v>
       </c>
       <c r="E17">
-        <v>195.278</v>
+        <v>208.5112</v>
       </c>
       <c r="F17">
-        <v>198.498</v>
+        <v>211.7312</v>
       </c>
       <c r="G17">
         <v>144.3</v>
@@ -2681,28 +2681,28 @@
         <v>203.1</v>
       </c>
       <c r="M17">
-        <v>9.984449399999999</v>
+        <v>10.65007936</v>
       </c>
       <c r="N17">
-        <v>193.1155506</v>
+        <v>192.44992064</v>
       </c>
       <c r="O17">
-        <v>67.59044270999999</v>
+        <v>67.35747222399999</v>
       </c>
       <c r="P17">
-        <v>125.52510789</v>
+        <v>125.092448416</v>
       </c>
       <c r="Q17">
-        <v>148.92510789</v>
+        <v>148.492448416</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08163010753753792</v>
+        <v>0.08192272683518084</v>
       </c>
       <c r="T17">
-        <v>0.6562410025640321</v>
+        <v>0.6616004277640147</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.34163245897165</v>
+        <v>19.07028043028592</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07404629054155192</v>
+        <v>0.07380273967619656</v>
       </c>
       <c r="C18">
-        <v>1154.057285631554</v>
+        <v>1143.61146015846</v>
       </c>
       <c r="D18">
-        <v>1221.488485631554</v>
+        <v>1224.27586015846</v>
       </c>
       <c r="E18">
-        <v>208.5112</v>
+        <v>221.7444</v>
       </c>
       <c r="F18">
-        <v>211.7312</v>
+        <v>224.9644</v>
       </c>
       <c r="G18">
         <v>144.3</v>
@@ -2763,28 +2763,28 @@
         <v>203.1</v>
       </c>
       <c r="M18">
-        <v>10.65007936</v>
+        <v>11.31570932</v>
       </c>
       <c r="N18">
-        <v>192.44992064</v>
+        <v>191.78429068</v>
       </c>
       <c r="O18">
-        <v>67.35747222399999</v>
+        <v>67.12450173799999</v>
       </c>
       <c r="P18">
-        <v>125.092448416</v>
+        <v>124.659788942</v>
       </c>
       <c r="Q18">
-        <v>148.492448416</v>
+        <v>148.059788942</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08192272683518084</v>
+        <v>0.08222239720023683</v>
       </c>
       <c r="T18">
-        <v>0.6616004277640147</v>
+        <v>0.6670889957399005</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.07028043028592</v>
+        <v>17.9484992285044</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07380273967619656</v>
+        <v>0.07355918881084124</v>
       </c>
       <c r="C19">
-        <v>1143.61146015846</v>
+        <v>1133.178385074583</v>
       </c>
       <c r="D19">
-        <v>1224.27586015846</v>
+        <v>1227.075985074583</v>
       </c>
       <c r="E19">
-        <v>221.7444</v>
+        <v>234.9776</v>
       </c>
       <c r="F19">
-        <v>224.9644</v>
+        <v>238.1976</v>
       </c>
       <c r="G19">
         <v>144.3</v>
@@ -2845,28 +2845,28 @@
         <v>203.1</v>
       </c>
       <c r="M19">
-        <v>11.31570932</v>
+        <v>11.98133928</v>
       </c>
       <c r="N19">
-        <v>191.78429068</v>
+        <v>191.11866072</v>
       </c>
       <c r="O19">
-        <v>67.12450173799999</v>
+        <v>66.89153125199999</v>
       </c>
       <c r="P19">
-        <v>124.659788942</v>
+        <v>124.227129468</v>
       </c>
       <c r="Q19">
-        <v>148.059788942</v>
+        <v>147.627129468</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08222239720023683</v>
+        <v>0.08252937659858688</v>
       </c>
       <c r="T19">
-        <v>0.6670889957399005</v>
+        <v>0.6727114312273933</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.9484992285044</v>
+        <v>16.95136038247637</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07355918881084125</v>
+        <v>0.07331563794548591</v>
       </c>
       <c r="C20">
-        <v>1133.178385074582</v>
+        <v>1122.758148067336</v>
       </c>
       <c r="D20">
-        <v>1227.075985074582</v>
+        <v>1229.888948067337</v>
       </c>
       <c r="E20">
-        <v>234.9776</v>
+        <v>248.2108</v>
       </c>
       <c r="F20">
-        <v>238.1976</v>
+        <v>251.4308</v>
       </c>
       <c r="G20">
         <v>144.3</v>
@@ -2927,28 +2927,28 @@
         <v>203.1</v>
       </c>
       <c r="M20">
-        <v>11.98133928</v>
+        <v>12.64696924</v>
       </c>
       <c r="N20">
-        <v>191.11866072</v>
+        <v>190.45303076</v>
       </c>
       <c r="O20">
-        <v>66.89153125199999</v>
+        <v>66.65856076599999</v>
       </c>
       <c r="P20">
-        <v>124.227129468</v>
+        <v>123.794469994</v>
       </c>
       <c r="Q20">
-        <v>147.627129468</v>
+        <v>147.194469994</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08252937659858688</v>
+        <v>0.0828439357351678</v>
       </c>
       <c r="T20">
-        <v>0.6727114312273933</v>
+        <v>0.6784726922824788</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.95136038247638</v>
+        <v>16.05918352024078</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07331563794548591</v>
+        <v>0.07307208708013059</v>
       </c>
       <c r="C21">
-        <v>1122.758148067336</v>
+        <v>1112.350837630044</v>
       </c>
       <c r="D21">
-        <v>1229.888948067337</v>
+        <v>1232.714837630044</v>
       </c>
       <c r="E21">
-        <v>248.2108</v>
+        <v>261.444</v>
       </c>
       <c r="F21">
-        <v>251.4308</v>
+        <v>264.664</v>
       </c>
       <c r="G21">
         <v>144.3</v>
@@ -3009,28 +3009,28 @@
         <v>203.1</v>
       </c>
       <c r="M21">
-        <v>12.64696924</v>
+        <v>13.3125992</v>
       </c>
       <c r="N21">
-        <v>190.45303076</v>
+        <v>189.7874008</v>
       </c>
       <c r="O21">
-        <v>66.65856076599999</v>
+        <v>66.42559027999999</v>
       </c>
       <c r="P21">
-        <v>123.794469994</v>
+        <v>123.36181052</v>
       </c>
       <c r="Q21">
-        <v>147.194469994</v>
+        <v>146.76181052</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0828439357351678</v>
+        <v>0.08316635885016323</v>
       </c>
       <c r="T21">
-        <v>0.6784726922824788</v>
+        <v>0.6843779848639411</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.05918352024078</v>
+        <v>15.25622434422874</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07307208708013059</v>
+        <v>0.07282853621477524</v>
       </c>
       <c r="C22">
-        <v>1112.350837630044</v>
+        <v>1101.95654307122</v>
       </c>
       <c r="D22">
-        <v>1232.714837630044</v>
+        <v>1235.55374307122</v>
       </c>
       <c r="E22">
-        <v>261.444</v>
+        <v>274.6772</v>
       </c>
       <c r="F22">
-        <v>264.664</v>
+        <v>277.8972</v>
       </c>
       <c r="G22">
         <v>144.3</v>
@@ -3091,28 +3091,28 @@
         <v>203.1</v>
       </c>
       <c r="M22">
-        <v>13.3125992</v>
+        <v>13.97822916</v>
       </c>
       <c r="N22">
-        <v>189.7874008</v>
+        <v>189.12177084</v>
       </c>
       <c r="O22">
-        <v>66.42559027999999</v>
+        <v>66.192619794</v>
       </c>
       <c r="P22">
-        <v>123.36181052</v>
+        <v>122.929151046</v>
       </c>
       <c r="Q22">
-        <v>146.76181052</v>
+        <v>146.329151046</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08316635885016323</v>
+        <v>0.08349694457566487</v>
       </c>
       <c r="T22">
-        <v>0.6843779848639411</v>
+        <v>0.6904327785234151</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.25622434422874</v>
+        <v>14.52973747069403</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07282853621477524</v>
+        <v>0.07258498534941993</v>
       </c>
       <c r="C23">
-        <v>1101.95654307122</v>
+        <v>1091.575354523974</v>
       </c>
       <c r="D23">
-        <v>1235.55374307122</v>
+        <v>1238.405754523974</v>
       </c>
       <c r="E23">
-        <v>274.6772</v>
+        <v>287.9104</v>
       </c>
       <c r="F23">
-        <v>277.8972</v>
+        <v>291.1304</v>
       </c>
       <c r="G23">
         <v>144.3</v>
@@ -3173,28 +3173,28 @@
         <v>203.1</v>
       </c>
       <c r="M23">
-        <v>13.97822916</v>
+        <v>14.64385912</v>
       </c>
       <c r="N23">
-        <v>189.12177084</v>
+        <v>188.45614088</v>
       </c>
       <c r="O23">
-        <v>66.192619794</v>
+        <v>65.959649308</v>
       </c>
       <c r="P23">
-        <v>122.929151046</v>
+        <v>122.496491572</v>
       </c>
       <c r="Q23">
-        <v>146.329151046</v>
+        <v>145.896491572</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08349694457566487</v>
+        <v>0.08383600685823067</v>
       </c>
       <c r="T23">
-        <v>0.6904327785234151</v>
+        <v>0.6966428233023629</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.52973747069403</v>
+        <v>13.86929485838976</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07258498534941993</v>
+        <v>0.07234143448406458</v>
       </c>
       <c r="C24">
-        <v>1091.575354523974</v>
+        <v>1081.207362955556</v>
       </c>
       <c r="D24">
-        <v>1238.405754523974</v>
+        <v>1241.270962955556</v>
       </c>
       <c r="E24">
-        <v>287.9104</v>
+        <v>301.1436</v>
       </c>
       <c r="F24">
-        <v>291.1304</v>
+        <v>304.3636</v>
       </c>
       <c r="G24">
         <v>144.3</v>
@@ -3255,28 +3255,28 @@
         <v>203.1</v>
       </c>
       <c r="M24">
-        <v>14.64385912</v>
+        <v>15.30948908</v>
       </c>
       <c r="N24">
-        <v>188.45614088</v>
+        <v>187.79051092</v>
       </c>
       <c r="O24">
-        <v>65.959649308</v>
+        <v>65.726678822</v>
       </c>
       <c r="P24">
-        <v>122.496491572</v>
+        <v>122.063832098</v>
       </c>
       <c r="Q24">
-        <v>145.896491572</v>
+        <v>145.463832098</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08383600685823067</v>
+        <v>0.08418387595333063</v>
       </c>
       <c r="T24">
-        <v>0.6966428233023629</v>
+        <v>0.7030141679456989</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.86929485838976</v>
+        <v>13.26628203845977</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07234143448406458</v>
+        <v>0.07233188361870925</v>
       </c>
       <c r="C25">
-        <v>1081.207362955556</v>
+        <v>1068.086792494337</v>
       </c>
       <c r="D25">
-        <v>1241.270962955556</v>
+        <v>1241.383592494337</v>
       </c>
       <c r="E25">
-        <v>301.1436</v>
+        <v>314.3768</v>
       </c>
       <c r="F25">
-        <v>304.3636</v>
+        <v>317.5968</v>
       </c>
       <c r="G25">
         <v>144.3</v>
@@ -3337,45 +3337,45 @@
         <v>203.1</v>
       </c>
       <c r="M25">
-        <v>15.30948908</v>
+        <v>16.45151424</v>
       </c>
       <c r="N25">
-        <v>187.79051092</v>
+        <v>186.64848576</v>
       </c>
       <c r="O25">
-        <v>65.726678822</v>
+        <v>65.32697001599999</v>
       </c>
       <c r="P25">
-        <v>122.063832098</v>
+        <v>121.321515744</v>
       </c>
       <c r="Q25">
-        <v>145.463832098</v>
+        <v>144.721515744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08418387595333063</v>
+        <v>0.08454089949830165</v>
       </c>
       <c r="T25">
-        <v>0.7030141679456989</v>
+        <v>0.7095531795533333</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.26628203845977</v>
+        <v>12.34536815499848</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07233188361870925</v>
+        <v>0.07209808275335394</v>
       </c>
       <c r="C26">
-        <v>1068.086792494337</v>
+        <v>1057.617101176176</v>
       </c>
       <c r="D26">
-        <v>1241.383592494337</v>
+        <v>1244.147101176176</v>
       </c>
       <c r="E26">
-        <v>314.3767999999999</v>
+        <v>327.61</v>
       </c>
       <c r="F26">
-        <v>317.5968</v>
+        <v>330.83</v>
       </c>
       <c r="G26">
         <v>144.3</v>
@@ -3419,28 +3419,28 @@
         <v>203.1</v>
       </c>
       <c r="M26">
-        <v>16.45151424</v>
+        <v>17.136994</v>
       </c>
       <c r="N26">
-        <v>186.64848576</v>
+        <v>185.963006</v>
       </c>
       <c r="O26">
-        <v>65.32697001599999</v>
+        <v>65.08705209999999</v>
       </c>
       <c r="P26">
-        <v>121.321515744</v>
+        <v>120.8759539</v>
       </c>
       <c r="Q26">
-        <v>144.721515744</v>
+        <v>144.2759539</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08454089949830165</v>
+        <v>0.08490744367113859</v>
       </c>
       <c r="T26">
-        <v>0.7095531795533333</v>
+        <v>0.716266564803838</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.34536815499848</v>
+        <v>11.85155342879854</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07209808275335394</v>
+        <v>0.07186428188799861</v>
       </c>
       <c r="C27">
-        <v>1057.617101176176</v>
+        <v>1047.15974129093</v>
       </c>
       <c r="D27">
-        <v>1244.147101176176</v>
+        <v>1246.92294129093</v>
       </c>
       <c r="E27">
-        <v>327.61</v>
+        <v>340.8432</v>
       </c>
       <c r="F27">
-        <v>330.83</v>
+        <v>344.0632</v>
       </c>
       <c r="G27">
         <v>144.3</v>
@@ -3501,28 +3501,28 @@
         <v>203.1</v>
       </c>
       <c r="M27">
-        <v>17.136994</v>
+        <v>17.82247376</v>
       </c>
       <c r="N27">
-        <v>185.963006</v>
+        <v>185.27752624</v>
       </c>
       <c r="O27">
-        <v>65.08705209999999</v>
+        <v>64.847134184</v>
       </c>
       <c r="P27">
-        <v>120.8759539</v>
+        <v>120.430392056</v>
       </c>
       <c r="Q27">
-        <v>144.2759539</v>
+        <v>143.830392056</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08490744367113859</v>
+        <v>0.08528389444324136</v>
       </c>
       <c r="T27">
-        <v>0.716266564803838</v>
+        <v>0.7231613928989508</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.85155342879854</v>
+        <v>11.39572445076783</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07186428188799861</v>
+        <v>0.07163048102264326</v>
       </c>
       <c r="C28">
-        <v>1047.15974129093</v>
+        <v>1036.714795561842</v>
       </c>
       <c r="D28">
-        <v>1246.92294129093</v>
+        <v>1249.711195561842</v>
       </c>
       <c r="E28">
-        <v>340.8432</v>
+        <v>354.0764</v>
       </c>
       <c r="F28">
-        <v>344.0632</v>
+        <v>357.2964</v>
       </c>
       <c r="G28">
         <v>144.3</v>
@@ -3583,28 +3583,28 @@
         <v>203.1</v>
       </c>
       <c r="M28">
-        <v>17.82247376</v>
+        <v>18.50795352</v>
       </c>
       <c r="N28">
-        <v>185.27752624</v>
+        <v>184.59204648</v>
       </c>
       <c r="O28">
-        <v>64.847134184</v>
+        <v>64.60721626799999</v>
       </c>
       <c r="P28">
-        <v>120.430392056</v>
+        <v>119.984830212</v>
       </c>
       <c r="Q28">
-        <v>143.830392056</v>
+        <v>143.384830212</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08528389444324136</v>
+        <v>0.08567065893512776</v>
       </c>
       <c r="T28">
-        <v>0.7231613928989508</v>
+        <v>0.7302451203939297</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.39572445076783</v>
+        <v>10.97366058222087</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07163048102264326</v>
+        <v>0.07139668015728795</v>
       </c>
       <c r="C29">
-        <v>1036.714795561842</v>
+        <v>1026.282347453727</v>
       </c>
       <c r="D29">
-        <v>1249.711195561842</v>
+        <v>1252.511947453728</v>
       </c>
       <c r="E29">
-        <v>354.0764</v>
+        <v>367.3096</v>
       </c>
       <c r="F29">
-        <v>357.2964</v>
+        <v>370.5296</v>
       </c>
       <c r="G29">
         <v>144.3</v>
@@ -3665,28 +3665,28 @@
         <v>203.1</v>
       </c>
       <c r="M29">
-        <v>18.50795352</v>
+        <v>19.19343328</v>
       </c>
       <c r="N29">
-        <v>184.59204648</v>
+        <v>183.90656672</v>
       </c>
       <c r="O29">
-        <v>64.60721626799999</v>
+        <v>64.36729835199999</v>
       </c>
       <c r="P29">
-        <v>119.984830212</v>
+        <v>119.539268368</v>
       </c>
       <c r="Q29">
-        <v>143.384830212</v>
+        <v>142.939268368</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08567065893512776</v>
+        <v>0.08606816688512214</v>
       </c>
       <c r="T29">
-        <v>0.7302451203939297</v>
+        <v>0.7375256180971025</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.97366058222087</v>
+        <v>10.58174413285584</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07139668015728795</v>
+        <v>0.07116287929193262</v>
       </c>
       <c r="C30">
-        <v>1026.282347453727</v>
+        <v>1015.862481181301</v>
       </c>
       <c r="D30">
-        <v>1252.511947453728</v>
+        <v>1255.325281181301</v>
       </c>
       <c r="E30">
-        <v>367.3096</v>
+        <v>380.5428</v>
       </c>
       <c r="F30">
-        <v>370.5296</v>
+        <v>383.7628</v>
       </c>
       <c r="G30">
         <v>144.3</v>
@@ -3747,28 +3747,28 @@
         <v>203.1</v>
       </c>
       <c r="M30">
-        <v>19.19343328</v>
+        <v>19.87891304</v>
       </c>
       <c r="N30">
-        <v>183.90656672</v>
+        <v>183.22108696</v>
       </c>
       <c r="O30">
-        <v>64.36729835199999</v>
+        <v>64.127380436</v>
       </c>
       <c r="P30">
-        <v>119.539268368</v>
+        <v>119.093706524</v>
       </c>
       <c r="Q30">
-        <v>142.939268368</v>
+        <v>142.493706524</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08606816688512214</v>
+        <v>0.08647687224215861</v>
       </c>
       <c r="T30">
-        <v>0.7375256180971025</v>
+        <v>0.7450112002426182</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.58174413285584</v>
+        <v>10.21685640413667</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07116287929193262</v>
+        <v>0.07092907842657728</v>
       </c>
       <c r="C31">
-        <v>1015.862481181301</v>
+        <v>1005.455281717617</v>
       </c>
       <c r="D31">
-        <v>1255.325281181301</v>
+        <v>1258.151281717617</v>
       </c>
       <c r="E31">
-        <v>380.5427999999999</v>
+        <v>393.776</v>
       </c>
       <c r="F31">
-        <v>383.7628</v>
+        <v>396.996</v>
       </c>
       <c r="G31">
         <v>144.3</v>
@@ -3829,28 +3829,28 @@
         <v>203.1</v>
       </c>
       <c r="M31">
-        <v>19.87891304</v>
+        <v>20.5643928</v>
       </c>
       <c r="N31">
-        <v>183.22108696</v>
+        <v>182.5356072</v>
       </c>
       <c r="O31">
-        <v>64.127380436</v>
+        <v>63.88746251999999</v>
       </c>
       <c r="P31">
-        <v>119.093706524</v>
+        <v>118.64814468</v>
       </c>
       <c r="Q31">
-        <v>142.493706524</v>
+        <v>142.04814468</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08647687224215861</v>
+        <v>0.0868972548951104</v>
       </c>
       <c r="T31">
-        <v>0.7450112002426182</v>
+        <v>0.75271065616372</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.21685640413667</v>
+        <v>9.876294523998782</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07092907842657728</v>
+        <v>0.07103782756122194</v>
       </c>
       <c r="C32">
-        <v>1005.455281717617</v>
+        <v>990.9060268223684</v>
       </c>
       <c r="D32">
-        <v>1258.151281717617</v>
+        <v>1256.835226822368</v>
       </c>
       <c r="E32">
-        <v>393.776</v>
+        <v>407.0092</v>
       </c>
       <c r="F32">
-        <v>396.996</v>
+        <v>410.2292</v>
       </c>
       <c r="G32">
         <v>144.3</v>
@@ -3911,45 +3911,45 @@
         <v>203.1</v>
       </c>
       <c r="M32">
-        <v>20.5643928</v>
+        <v>21.9472622</v>
       </c>
       <c r="N32">
-        <v>182.5356072</v>
+        <v>181.1527378</v>
       </c>
       <c r="O32">
-        <v>63.88746251999999</v>
+        <v>63.40345822999999</v>
       </c>
       <c r="P32">
-        <v>118.64814468</v>
+        <v>117.74927957</v>
       </c>
       <c r="Q32">
-        <v>142.04814468</v>
+        <v>141.14927957</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0868972548951104</v>
+        <v>0.08732982255249558</v>
       </c>
       <c r="T32">
-        <v>0.75271065616372</v>
+        <v>0.7606332847202163</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.35</v>
       </c>
       <c r="W32">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>9.876294523998782</v>
+        <v>9.254001622124877</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07103782756122194</v>
+        <v>0.07081507669586662</v>
       </c>
       <c r="C33">
-        <v>990.9060268223684</v>
+        <v>980.3714644983839</v>
       </c>
       <c r="D33">
-        <v>1256.835226822368</v>
+        <v>1259.533864498384</v>
       </c>
       <c r="E33">
-        <v>407.0092</v>
+        <v>420.2424</v>
       </c>
       <c r="F33">
-        <v>410.2292</v>
+        <v>423.4624</v>
       </c>
       <c r="G33">
         <v>144.3</v>
@@ -3993,28 +3993,28 @@
         <v>203.1</v>
       </c>
       <c r="M33">
-        <v>21.9472622</v>
+        <v>22.6552384</v>
       </c>
       <c r="N33">
-        <v>181.1527378</v>
+        <v>180.4447616</v>
       </c>
       <c r="O33">
-        <v>63.40345822999999</v>
+        <v>63.15566655999999</v>
       </c>
       <c r="P33">
-        <v>117.74927957</v>
+        <v>117.28909504</v>
       </c>
       <c r="Q33">
-        <v>141.14927957</v>
+        <v>140.68909504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08732982255249558</v>
+        <v>0.08777511278803915</v>
       </c>
       <c r="T33">
-        <v>0.7606332847202163</v>
+        <v>0.7687889317636681</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.254001622124877</v>
+        <v>8.964814071433475</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07081507669586662</v>
+        <v>0.07059232583051128</v>
       </c>
       <c r="C34">
-        <v>980.3714644983839</v>
+        <v>969.8485159736774</v>
       </c>
       <c r="D34">
-        <v>1259.533864498384</v>
+        <v>1262.244115973677</v>
       </c>
       <c r="E34">
-        <v>420.2424</v>
+        <v>433.4756</v>
       </c>
       <c r="F34">
-        <v>423.4624</v>
+        <v>436.6956</v>
       </c>
       <c r="G34">
         <v>144.3</v>
@@ -4075,28 +4075,28 @@
         <v>203.1</v>
       </c>
       <c r="M34">
-        <v>22.6552384</v>
+        <v>23.3632146</v>
       </c>
       <c r="N34">
-        <v>180.4447616</v>
+        <v>179.7367854</v>
       </c>
       <c r="O34">
-        <v>63.15566655999999</v>
+        <v>62.90787489</v>
       </c>
       <c r="P34">
-        <v>117.28909504</v>
+        <v>116.82891051</v>
       </c>
       <c r="Q34">
-        <v>140.68909504</v>
+        <v>140.22891051</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08777511278803915</v>
+        <v>0.08823369526941983</v>
       </c>
       <c r="T34">
-        <v>0.7687889317636681</v>
+        <v>0.7771880309576708</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.964814071433475</v>
+        <v>8.693153038965793</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07059232583051128</v>
+        <v>0.07036957496515595</v>
       </c>
       <c r="C35">
-        <v>969.8485159736774</v>
+        <v>959.3372563812651</v>
       </c>
       <c r="D35">
-        <v>1262.244115973677</v>
+        <v>1264.966056381265</v>
       </c>
       <c r="E35">
-        <v>433.4756</v>
+        <v>446.7088</v>
       </c>
       <c r="F35">
-        <v>436.6956</v>
+        <v>449.9288</v>
       </c>
       <c r="G35">
         <v>144.3</v>
@@ -4157,28 +4157,28 @@
         <v>203.1</v>
       </c>
       <c r="M35">
-        <v>23.3632146</v>
+        <v>24.0711908</v>
       </c>
       <c r="N35">
-        <v>179.7367854</v>
+        <v>179.0288092</v>
       </c>
       <c r="O35">
-        <v>62.90787489</v>
+        <v>62.66008321999999</v>
       </c>
       <c r="P35">
-        <v>116.82891051</v>
+        <v>116.36872598</v>
       </c>
       <c r="Q35">
-        <v>140.22891051</v>
+        <v>139.76872598</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08823369526941983</v>
+        <v>0.08870617418963024</v>
       </c>
       <c r="T35">
-        <v>0.7771880309576708</v>
+        <v>0.7858416483090676</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.693153038965793</v>
+        <v>8.437472067231505</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07036957496515595</v>
+        <v>0.07014682409980062</v>
       </c>
       <c r="C36">
-        <v>959.3372563812651</v>
+        <v>948.8377615036406</v>
       </c>
       <c r="D36">
-        <v>1264.966056381265</v>
+        <v>1267.699761503641</v>
       </c>
       <c r="E36">
-        <v>446.7088</v>
+        <v>459.942</v>
       </c>
       <c r="F36">
-        <v>449.9288</v>
+        <v>463.162</v>
       </c>
       <c r="G36">
         <v>144.3</v>
@@ -4239,28 +4239,28 @@
         <v>203.1</v>
       </c>
       <c r="M36">
-        <v>24.0711908</v>
+        <v>24.779167</v>
       </c>
       <c r="N36">
-        <v>179.0288092</v>
+        <v>178.320833</v>
       </c>
       <c r="O36">
-        <v>62.66008321999999</v>
+        <v>62.41229154999999</v>
       </c>
       <c r="P36">
-        <v>116.36872598</v>
+        <v>115.90854145</v>
       </c>
       <c r="Q36">
-        <v>139.76872598</v>
+        <v>139.30854145</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08870617418963024</v>
+        <v>0.0891931909227702</v>
       </c>
       <c r="T36">
-        <v>0.7858416483090676</v>
+        <v>0.794761530809738</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.437472067231505</v>
+        <v>8.196401436739176</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07014682409980062</v>
+        <v>0.0699240732344453</v>
       </c>
       <c r="C37">
-        <v>948.8377615036406</v>
+        <v>938.3501077798081</v>
       </c>
       <c r="D37">
-        <v>1267.699761503641</v>
+        <v>1270.445307779808</v>
       </c>
       <c r="E37">
-        <v>459.942</v>
+        <v>473.1752</v>
       </c>
       <c r="F37">
-        <v>463.162</v>
+        <v>476.3952</v>
       </c>
       <c r="G37">
         <v>144.3</v>
@@ -4321,28 +4321,28 @@
         <v>203.1</v>
       </c>
       <c r="M37">
-        <v>24.779167</v>
+        <v>25.4871432</v>
       </c>
       <c r="N37">
-        <v>178.320833</v>
+        <v>177.6128568</v>
       </c>
       <c r="O37">
-        <v>62.41229154999999</v>
+        <v>62.16449987999999</v>
       </c>
       <c r="P37">
-        <v>115.90854145</v>
+        <v>115.44835692</v>
       </c>
       <c r="Q37">
-        <v>139.30854145</v>
+        <v>138.84835692</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0891931909227702</v>
+        <v>0.08969542692882078</v>
       </c>
       <c r="T37">
-        <v>0.794761530809738</v>
+        <v>0.8039601596385544</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.196401436739176</v>
+        <v>7.968723619051977</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0699240732344453</v>
+        <v>0.06970132236908998</v>
       </c>
       <c r="C38">
-        <v>938.3501077798082</v>
+        <v>927.8743723124054</v>
       </c>
       <c r="D38">
-        <v>1270.445307779808</v>
+        <v>1273.202772312405</v>
       </c>
       <c r="E38">
-        <v>473.1751999999999</v>
+        <v>486.4083999999999</v>
       </c>
       <c r="F38">
-        <v>476.3951999999999</v>
+        <v>489.6283999999999</v>
       </c>
       <c r="G38">
         <v>144.3</v>
@@ -4403,28 +4403,28 @@
         <v>203.1</v>
       </c>
       <c r="M38">
-        <v>25.48714319999999</v>
+        <v>26.1951194</v>
       </c>
       <c r="N38">
-        <v>177.6128568</v>
+        <v>176.9048806</v>
       </c>
       <c r="O38">
-        <v>62.16449987999999</v>
+        <v>61.91670821</v>
       </c>
       <c r="P38">
-        <v>115.44835692</v>
+        <v>114.98817239</v>
       </c>
       <c r="Q38">
-        <v>138.84835692</v>
+        <v>138.38817239</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08969542692882078</v>
+        <v>0.09021360693506345</v>
       </c>
       <c r="T38">
-        <v>0.8039601596385544</v>
+        <v>0.8134508084301904</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.968723619051979</v>
+        <v>7.753352710428953</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06970132236908998</v>
+        <v>0.06967617150373463</v>
       </c>
       <c r="C39">
-        <v>927.8743723124054</v>
+        <v>914.9532706924394</v>
       </c>
       <c r="D39">
-        <v>1273.202772312405</v>
+        <v>1273.514870692439</v>
       </c>
       <c r="E39">
-        <v>486.4083999999999</v>
+        <v>499.6416</v>
       </c>
       <c r="F39">
-        <v>489.6283999999999</v>
+        <v>502.8616</v>
       </c>
       <c r="G39">
         <v>144.3</v>
@@ -4485,45 +4485,45 @@
         <v>203.1</v>
       </c>
       <c r="M39">
-        <v>26.1951194</v>
+        <v>27.30538488</v>
       </c>
       <c r="N39">
-        <v>176.9048806</v>
+        <v>175.79461512</v>
       </c>
       <c r="O39">
-        <v>61.91670821</v>
+        <v>61.528115292</v>
       </c>
       <c r="P39">
-        <v>114.98817239</v>
+        <v>114.266499828</v>
       </c>
       <c r="Q39">
-        <v>138.38817239</v>
+        <v>137.666499828</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09021360693506345</v>
+        <v>0.09074850242537845</v>
       </c>
       <c r="T39">
-        <v>0.8134508084301904</v>
+        <v>0.8232476071828468</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.753352710428953</v>
+        <v>7.43809328791999</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06967617150373463</v>
+        <v>0.06945862063837932</v>
       </c>
       <c r="C40">
-        <v>914.9532706924394</v>
+        <v>904.4260698935635</v>
       </c>
       <c r="D40">
-        <v>1273.514870692439</v>
+        <v>1276.220869893564</v>
       </c>
       <c r="E40">
-        <v>499.6416</v>
+        <v>512.8747999999999</v>
       </c>
       <c r="F40">
-        <v>502.8616</v>
+        <v>516.0948</v>
       </c>
       <c r="G40">
         <v>144.3</v>
@@ -4567,28 +4567,28 @@
         <v>203.1</v>
       </c>
       <c r="M40">
-        <v>27.30538488</v>
+        <v>28.02394764</v>
       </c>
       <c r="N40">
-        <v>175.79461512</v>
+        <v>175.07605236</v>
       </c>
       <c r="O40">
-        <v>61.528115292</v>
+        <v>61.276618326</v>
       </c>
       <c r="P40">
-        <v>114.266499828</v>
+        <v>113.799434034</v>
       </c>
       <c r="Q40">
-        <v>137.666499828</v>
+        <v>137.199434034</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09074850242537845</v>
+        <v>0.09130093547275298</v>
       </c>
       <c r="T40">
-        <v>0.8232476071828468</v>
+        <v>0.833365612451984</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.43809328791999</v>
+        <v>7.247372947204094</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06945862063837932</v>
+        <v>0.06924106977302398</v>
       </c>
       <c r="C41">
-        <v>904.4260698935635</v>
+        <v>893.9103931434117</v>
       </c>
       <c r="D41">
-        <v>1276.220869893564</v>
+        <v>1278.938393143412</v>
       </c>
       <c r="E41">
-        <v>512.8747999999999</v>
+        <v>526.1079999999999</v>
       </c>
       <c r="F41">
-        <v>516.0948</v>
+        <v>529.328</v>
       </c>
       <c r="G41">
         <v>144.3</v>
@@ -4649,28 +4649,28 @@
         <v>203.1</v>
       </c>
       <c r="M41">
-        <v>28.02394764</v>
+        <v>28.7425104</v>
       </c>
       <c r="N41">
-        <v>175.07605236</v>
+        <v>174.3574896</v>
       </c>
       <c r="O41">
-        <v>61.276618326</v>
+        <v>61.02512136</v>
       </c>
       <c r="P41">
-        <v>113.799434034</v>
+        <v>113.33236824</v>
       </c>
       <c r="Q41">
-        <v>137.199434034</v>
+        <v>136.73236824</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09130093547275298</v>
+        <v>0.09187178295503996</v>
       </c>
       <c r="T41">
-        <v>0.833365612451984</v>
+        <v>0.8438208845634255</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.247372947204094</v>
+        <v>7.066188623523991</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06924106977302398</v>
+        <v>0.06902351890766864</v>
       </c>
       <c r="C42">
-        <v>893.9103931434117</v>
+        <v>883.4063142153351</v>
       </c>
       <c r="D42">
-        <v>1278.938393143412</v>
+        <v>1281.667514215335</v>
       </c>
       <c r="E42">
-        <v>526.1079999999999</v>
+        <v>539.3412</v>
       </c>
       <c r="F42">
-        <v>529.328</v>
+        <v>542.5612</v>
       </c>
       <c r="G42">
         <v>144.3</v>
@@ -4731,28 +4731,28 @@
         <v>203.1</v>
       </c>
       <c r="M42">
-        <v>28.7425104</v>
+        <v>29.46107316</v>
       </c>
       <c r="N42">
-        <v>174.3574896</v>
+        <v>173.63892684</v>
       </c>
       <c r="O42">
-        <v>61.02512136</v>
+        <v>60.77362439399999</v>
       </c>
       <c r="P42">
-        <v>113.33236824</v>
+        <v>112.865302446</v>
       </c>
       <c r="Q42">
-        <v>136.73236824</v>
+        <v>136.265302446</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09187178295503996</v>
+        <v>0.09246198119943838</v>
       </c>
       <c r="T42">
-        <v>0.8438208845634255</v>
+        <v>0.8546305726786448</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.066188623523991</v>
+        <v>6.8938425595356</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06902351890766864</v>
+        <v>0.06880596804231331</v>
       </c>
       <c r="C43">
-        <v>883.4063142153351</v>
+        <v>872.9139075137314</v>
       </c>
       <c r="D43">
-        <v>1281.667514215335</v>
+        <v>1284.408307513731</v>
       </c>
       <c r="E43">
-        <v>539.3412</v>
+        <v>552.5744</v>
       </c>
       <c r="F43">
-        <v>542.5612</v>
+        <v>555.7944</v>
       </c>
       <c r="G43">
         <v>144.3</v>
@@ -4813,28 +4813,28 @@
         <v>203.1</v>
       </c>
       <c r="M43">
-        <v>29.46107316</v>
+        <v>30.17963592</v>
       </c>
       <c r="N43">
-        <v>173.63892684</v>
+        <v>172.92036408</v>
       </c>
       <c r="O43">
-        <v>60.77362439399999</v>
+        <v>60.52212742799999</v>
       </c>
       <c r="P43">
-        <v>112.865302446</v>
+        <v>112.398236652</v>
       </c>
       <c r="Q43">
-        <v>136.265302446</v>
+        <v>135.798236652</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09246198119943838</v>
+        <v>0.09307253110743675</v>
       </c>
       <c r="T43">
-        <v>0.8546305726786448</v>
+        <v>0.8658130086599061</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.8938425595356</v>
+        <v>6.729703450975229</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06880596804231331</v>
+        <v>0.068588417176958</v>
       </c>
       <c r="C44">
-        <v>872.9139075137314</v>
+        <v>862.4332480808047</v>
       </c>
       <c r="D44">
-        <v>1284.408307513731</v>
+        <v>1287.160848080805</v>
       </c>
       <c r="E44">
-        <v>552.5744</v>
+        <v>565.8076</v>
       </c>
       <c r="F44">
-        <v>555.7944</v>
+        <v>569.0276</v>
       </c>
       <c r="G44">
         <v>144.3</v>
@@ -4895,28 +4895,28 @@
         <v>203.1</v>
       </c>
       <c r="M44">
-        <v>30.17963592</v>
+        <v>30.89819868</v>
       </c>
       <c r="N44">
-        <v>172.92036408</v>
+        <v>172.20180132</v>
       </c>
       <c r="O44">
-        <v>60.52212742799999</v>
+        <v>60.27063046199999</v>
       </c>
       <c r="P44">
-        <v>112.398236652</v>
+        <v>111.931170858</v>
       </c>
       <c r="Q44">
-        <v>135.798236652</v>
+        <v>135.331170858</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09307253110743675</v>
+        <v>0.09370450381922454</v>
       </c>
       <c r="T44">
-        <v>0.8658130086599061</v>
+        <v>0.8773878108159486</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.729703450975229</v>
+        <v>6.573198719557201</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.068588417176958</v>
+        <v>0.06837086631160266</v>
       </c>
       <c r="C45">
-        <v>862.4332480808047</v>
+        <v>851.9644116034156</v>
       </c>
       <c r="D45">
-        <v>1287.160848080805</v>
+        <v>1289.925211603416</v>
       </c>
       <c r="E45">
-        <v>565.8076</v>
+        <v>579.0408</v>
       </c>
       <c r="F45">
-        <v>569.0276</v>
+        <v>582.2608</v>
       </c>
       <c r="G45">
         <v>144.3</v>
@@ -4977,28 +4977,28 @@
         <v>203.1</v>
       </c>
       <c r="M45">
-        <v>30.89819868</v>
+        <v>31.61676144</v>
       </c>
       <c r="N45">
-        <v>172.20180132</v>
+        <v>171.48323856</v>
       </c>
       <c r="O45">
-        <v>60.27063046199999</v>
+        <v>60.01913349599999</v>
       </c>
       <c r="P45">
-        <v>111.931170858</v>
+        <v>111.464105064</v>
       </c>
       <c r="Q45">
-        <v>135.331170858</v>
+        <v>134.864105064</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09370450381922454</v>
+        <v>0.09435904698500475</v>
       </c>
       <c r="T45">
-        <v>0.8773878108159486</v>
+        <v>0.8893759987632782</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.573198719557201</v>
+        <v>6.423807839567264</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06837086631160266</v>
+        <v>0.06815331544624734</v>
       </c>
       <c r="C46">
-        <v>851.9644116034156</v>
+        <v>841.507474420017</v>
       </c>
       <c r="D46">
-        <v>1289.925211603416</v>
+        <v>1292.701474420017</v>
       </c>
       <c r="E46">
-        <v>579.0408</v>
+        <v>592.274</v>
       </c>
       <c r="F46">
-        <v>582.2608</v>
+        <v>595.494</v>
       </c>
       <c r="G46">
         <v>144.3</v>
@@ -5059,28 +5059,28 @@
         <v>203.1</v>
       </c>
       <c r="M46">
-        <v>31.61676144</v>
+        <v>32.3353242</v>
       </c>
       <c r="N46">
-        <v>171.48323856</v>
+        <v>170.7646758</v>
       </c>
       <c r="O46">
-        <v>60.01913349599999</v>
+        <v>59.76763652999999</v>
       </c>
       <c r="P46">
-        <v>111.464105064</v>
+        <v>110.99703927</v>
       </c>
       <c r="Q46">
-        <v>134.864105064</v>
+        <v>134.39703927</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09435904698500475</v>
+        <v>0.09503739172044968</v>
       </c>
       <c r="T46">
-        <v>0.8893759987632782</v>
+        <v>0.9018001208177835</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.423807839567264</v>
+        <v>6.281056554243547</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06815331544624734</v>
+        <v>0.06793576458089201</v>
       </c>
       <c r="C47">
-        <v>841.507474420017</v>
+        <v>831.0625135276825</v>
       </c>
       <c r="D47">
-        <v>1292.701474420017</v>
+        <v>1295.489713527683</v>
       </c>
       <c r="E47">
-        <v>592.274</v>
+        <v>605.5072</v>
       </c>
       <c r="F47">
-        <v>595.494</v>
+        <v>608.7272</v>
       </c>
       <c r="G47">
         <v>144.3</v>
@@ -5141,28 +5141,28 @@
         <v>203.1</v>
       </c>
       <c r="M47">
-        <v>32.3353242</v>
+        <v>33.05388696</v>
       </c>
       <c r="N47">
-        <v>170.7646758</v>
+        <v>170.04611304</v>
       </c>
       <c r="O47">
-        <v>59.76763652999999</v>
+        <v>59.51613956399999</v>
       </c>
       <c r="P47">
-        <v>110.99703927</v>
+        <v>110.529973476</v>
       </c>
       <c r="Q47">
-        <v>134.39703927</v>
+        <v>133.929973476</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09503739172044968</v>
+        <v>0.09574086033498519</v>
       </c>
       <c r="T47">
-        <v>0.9018001208177835</v>
+        <v>0.9146843955409742</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.281056554243547</v>
+        <v>6.144511846542601</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06793576458089201</v>
+        <v>0.06802371371553667</v>
       </c>
       <c r="C48">
-        <v>831.0625135276825</v>
+        <v>816.7006669552499</v>
       </c>
       <c r="D48">
-        <v>1295.489713527683</v>
+        <v>1294.36106695525</v>
       </c>
       <c r="E48">
-        <v>605.5072</v>
+        <v>618.7404</v>
       </c>
       <c r="F48">
-        <v>608.7272</v>
+        <v>621.9604</v>
       </c>
       <c r="G48">
         <v>144.3</v>
@@ -5223,45 +5223,45 @@
         <v>203.1</v>
       </c>
       <c r="M48">
-        <v>33.05388696</v>
+        <v>34.39441012</v>
       </c>
       <c r="N48">
-        <v>170.04611304</v>
+        <v>168.70558988</v>
       </c>
       <c r="O48">
-        <v>59.51613956399999</v>
+        <v>59.04695645799999</v>
       </c>
       <c r="P48">
-        <v>110.529973476</v>
+        <v>109.658633422</v>
       </c>
       <c r="Q48">
-        <v>133.929973476</v>
+        <v>133.058633422</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09574086033498519</v>
+        <v>0.09647087493497485</v>
       </c>
       <c r="T48">
-        <v>0.9146843955409742</v>
+        <v>0.928054869310323</v>
       </c>
       <c r="U48">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.35</v>
       </c>
       <c r="W48">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>6.144511846542601</v>
+        <v>5.905029314106462</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06802371371553667</v>
+        <v>0.06781266285018135</v>
       </c>
       <c r="C49">
-        <v>816.7006669552499</v>
+        <v>806.1791811246801</v>
       </c>
       <c r="D49">
-        <v>1294.36106695525</v>
+        <v>1297.07278112468</v>
       </c>
       <c r="E49">
-        <v>618.7404</v>
+        <v>631.9736</v>
       </c>
       <c r="F49">
-        <v>621.9604</v>
+        <v>635.1936000000001</v>
       </c>
       <c r="G49">
         <v>144.3</v>
@@ -5305,28 +5305,28 @@
         <v>203.1</v>
       </c>
       <c r="M49">
-        <v>34.39441012</v>
+        <v>35.12620608</v>
       </c>
       <c r="N49">
-        <v>168.70558988</v>
+        <v>167.97379392</v>
       </c>
       <c r="O49">
-        <v>59.04695645799999</v>
+        <v>58.79082787199999</v>
       </c>
       <c r="P49">
-        <v>109.658633422</v>
+        <v>109.182966048</v>
       </c>
       <c r="Q49">
-        <v>133.058633422</v>
+        <v>132.582966048</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09647087493497485</v>
+        <v>0.0972289670195795</v>
       </c>
       <c r="T49">
-        <v>0.928054869310323</v>
+        <v>0.9419395920708006</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.905029314106462</v>
+        <v>5.782007870062578</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06781266285018134</v>
+        <v>0.067601611984826</v>
       </c>
       <c r="C50">
-        <v>806.1791811246802</v>
+        <v>795.6690813467121</v>
       </c>
       <c r="D50">
-        <v>1297.07278112468</v>
+        <v>1299.795881346712</v>
       </c>
       <c r="E50">
-        <v>631.9735999999999</v>
+        <v>645.2067999999999</v>
       </c>
       <c r="F50">
-        <v>635.1935999999999</v>
+        <v>648.4268</v>
       </c>
       <c r="G50">
         <v>144.3</v>
@@ -5387,28 +5387,28 @@
         <v>203.1</v>
       </c>
       <c r="M50">
-        <v>35.12620608</v>
+        <v>35.85800204</v>
       </c>
       <c r="N50">
-        <v>167.97379392</v>
+        <v>167.24199796</v>
       </c>
       <c r="O50">
-        <v>58.79082787199999</v>
+        <v>58.53469928599999</v>
       </c>
       <c r="P50">
-        <v>109.182966048</v>
+        <v>108.707298674</v>
       </c>
       <c r="Q50">
-        <v>132.582966048</v>
+        <v>132.107298674</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0972289670195795</v>
+        <v>0.09801678820554119</v>
       </c>
       <c r="T50">
-        <v>0.9419395920708006</v>
+        <v>0.9563688137630616</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.782007870062579</v>
+        <v>5.664007709449056</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.067601611984826</v>
+        <v>0.06739056111947067</v>
       </c>
       <c r="C51">
-        <v>795.6690813467121</v>
+        <v>785.1704394845277</v>
       </c>
       <c r="D51">
-        <v>1299.795881346712</v>
+        <v>1302.530439484528</v>
       </c>
       <c r="E51">
-        <v>645.2067999999999</v>
+        <v>658.4399999999999</v>
       </c>
       <c r="F51">
-        <v>648.4268</v>
+        <v>661.66</v>
       </c>
       <c r="G51">
         <v>144.3</v>
@@ -5469,28 +5469,28 @@
         <v>203.1</v>
       </c>
       <c r="M51">
-        <v>35.85800204</v>
+        <v>36.589798</v>
       </c>
       <c r="N51">
-        <v>167.24199796</v>
+        <v>166.510202</v>
       </c>
       <c r="O51">
-        <v>58.53469928599999</v>
+        <v>58.2785707</v>
       </c>
       <c r="P51">
-        <v>108.707298674</v>
+        <v>108.2316313</v>
       </c>
       <c r="Q51">
-        <v>132.107298674</v>
+        <v>131.6316313</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09801678820554119</v>
+        <v>0.09883612223894135</v>
       </c>
       <c r="T51">
-        <v>0.9563688137630616</v>
+        <v>0.9713752043230131</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.664007709449056</v>
+        <v>5.550727555260075</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06739056111947067</v>
+        <v>0.06717951025411535</v>
       </c>
       <c r="C52">
-        <v>785.1704394845277</v>
+        <v>774.6833280073374</v>
       </c>
       <c r="D52">
-        <v>1302.530439484528</v>
+        <v>1305.276528007337</v>
       </c>
       <c r="E52">
-        <v>658.4399999999999</v>
+        <v>671.6732</v>
       </c>
       <c r="F52">
-        <v>661.66</v>
+        <v>674.8932</v>
       </c>
       <c r="G52">
         <v>144.3</v>
@@ -5551,28 +5551,28 @@
         <v>203.1</v>
       </c>
       <c r="M52">
-        <v>36.589798</v>
+        <v>37.32159396</v>
       </c>
       <c r="N52">
-        <v>166.510202</v>
+        <v>165.77840604</v>
       </c>
       <c r="O52">
-        <v>58.2785707</v>
+        <v>58.02244211399999</v>
       </c>
       <c r="P52">
-        <v>108.2316313</v>
+        <v>107.755963926</v>
       </c>
       <c r="Q52">
-        <v>131.6316313</v>
+        <v>131.155963926</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09883612223894135</v>
+        <v>0.09968889847778642</v>
       </c>
       <c r="T52">
-        <v>0.9713752043230131</v>
+        <v>0.9869941006201054</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.550727555260075</v>
+        <v>5.441889760058897</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06717951025411535</v>
+        <v>0.06696845938876002</v>
       </c>
       <c r="C53">
-        <v>774.6833280073374</v>
+        <v>764.2078199967835</v>
       </c>
       <c r="D53">
-        <v>1305.276528007337</v>
+        <v>1308.034219996784</v>
       </c>
       <c r="E53">
-        <v>671.6732</v>
+        <v>684.9064</v>
       </c>
       <c r="F53">
-        <v>674.8932</v>
+        <v>688.1264</v>
       </c>
       <c r="G53">
         <v>144.3</v>
@@ -5633,28 +5633,28 @@
         <v>203.1</v>
       </c>
       <c r="M53">
-        <v>37.32159396</v>
+        <v>38.05338992</v>
       </c>
       <c r="N53">
-        <v>165.77840604</v>
+        <v>165.04661008</v>
       </c>
       <c r="O53">
-        <v>58.02244211399999</v>
+        <v>57.76631352799999</v>
       </c>
       <c r="P53">
-        <v>107.755963926</v>
+        <v>107.280296552</v>
       </c>
       <c r="Q53">
-        <v>131.155963926</v>
+        <v>130.680296552</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09968889847778642</v>
+        <v>0.1005772070599167</v>
       </c>
       <c r="T53">
-        <v>0.9869941006201054</v>
+        <v>1.00326378426291</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.441889760058897</v>
+        <v>5.337238033903919</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06696845938876002</v>
+        <v>0.06675740852340468</v>
       </c>
       <c r="C54">
-        <v>764.2078199967835</v>
+        <v>753.7439891534204</v>
       </c>
       <c r="D54">
-        <v>1308.034219996784</v>
+        <v>1310.80358915342</v>
       </c>
       <c r="E54">
-        <v>684.9064</v>
+        <v>698.1396</v>
       </c>
       <c r="F54">
-        <v>688.1264</v>
+        <v>701.3596</v>
       </c>
       <c r="G54">
         <v>144.3</v>
@@ -5715,28 +5715,28 @@
         <v>203.1</v>
       </c>
       <c r="M54">
-        <v>38.05338992</v>
+        <v>38.78518588</v>
       </c>
       <c r="N54">
-        <v>165.04661008</v>
+        <v>164.31481412</v>
       </c>
       <c r="O54">
-        <v>57.76631352799999</v>
+        <v>57.510184942</v>
       </c>
       <c r="P54">
-        <v>107.280296552</v>
+        <v>106.804629178</v>
       </c>
       <c r="Q54">
-        <v>130.680296552</v>
+        <v>130.204629178</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1005772070599167</v>
+        <v>0.101503316007244</v>
       </c>
       <c r="T54">
-        <v>1.00326378426291</v>
+        <v>1.020225794869238</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.337238033903919</v>
+        <v>5.236535429490637</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06675740852340468</v>
+        <v>0.06654635765804937</v>
       </c>
       <c r="C55">
-        <v>753.7439891534204</v>
+        <v>743.291909803282</v>
       </c>
       <c r="D55">
-        <v>1310.80358915342</v>
+        <v>1313.584709803282</v>
       </c>
       <c r="E55">
-        <v>698.1396</v>
+        <v>711.3728</v>
       </c>
       <c r="F55">
-        <v>701.3596</v>
+        <v>714.5928</v>
       </c>
       <c r="G55">
         <v>144.3</v>
@@ -5797,28 +5797,28 @@
         <v>203.1</v>
       </c>
       <c r="M55">
-        <v>38.78518588</v>
+        <v>39.51698184</v>
       </c>
       <c r="N55">
-        <v>164.31481412</v>
+        <v>163.58301816</v>
       </c>
       <c r="O55">
-        <v>57.510184942</v>
+        <v>57.25405635599999</v>
       </c>
       <c r="P55">
-        <v>106.804629178</v>
+        <v>106.328961804</v>
       </c>
       <c r="Q55">
-        <v>130.204629178</v>
+        <v>129.728961804</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.101503316007244</v>
+        <v>0.1024696905609769</v>
       </c>
       <c r="T55">
-        <v>1.020225794869238</v>
+        <v>1.037925284197581</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.236535429490637</v>
+        <v>5.139562551166737</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06654635765804937</v>
+        <v>0.06633530679269403</v>
       </c>
       <c r="C56">
-        <v>743.291909803282</v>
+        <v>732.8516569045316</v>
       </c>
       <c r="D56">
-        <v>1313.584709803282</v>
+        <v>1316.377656904532</v>
       </c>
       <c r="E56">
-        <v>711.3728</v>
+        <v>724.606</v>
       </c>
       <c r="F56">
-        <v>714.5928</v>
+        <v>727.826</v>
       </c>
       <c r="G56">
         <v>144.3</v>
@@ -5879,28 +5879,28 @@
         <v>203.1</v>
       </c>
       <c r="M56">
-        <v>39.51698184</v>
+        <v>40.2487778</v>
       </c>
       <c r="N56">
-        <v>163.58301816</v>
+        <v>162.8512222</v>
       </c>
       <c r="O56">
-        <v>57.25405635599999</v>
+        <v>56.99792777</v>
       </c>
       <c r="P56">
-        <v>106.328961804</v>
+        <v>105.85329443</v>
       </c>
       <c r="Q56">
-        <v>129.728961804</v>
+        <v>129.25329443</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1024696905609769</v>
+        <v>0.1034790150948756</v>
       </c>
       <c r="T56">
-        <v>1.037925284197581</v>
+        <v>1.056411417496072</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.139562551166737</v>
+        <v>5.046115959327341</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06633530679269403</v>
+        <v>0.0661242559273387</v>
       </c>
       <c r="C57">
-        <v>732.8516569045316</v>
+        <v>722.4233060541957</v>
       </c>
       <c r="D57">
-        <v>1316.377656904532</v>
+        <v>1319.182506054196</v>
       </c>
       <c r="E57">
-        <v>724.606</v>
+        <v>737.8392</v>
       </c>
       <c r="F57">
-        <v>727.826</v>
+        <v>741.0592</v>
       </c>
       <c r="G57">
         <v>144.3</v>
@@ -5961,28 +5961,28 @@
         <v>203.1</v>
       </c>
       <c r="M57">
-        <v>40.2487778</v>
+        <v>40.98057376000001</v>
       </c>
       <c r="N57">
-        <v>162.8512222</v>
+        <v>162.11942624</v>
       </c>
       <c r="O57">
-        <v>56.99792777</v>
+        <v>56.74179918399999</v>
       </c>
       <c r="P57">
-        <v>105.85329443</v>
+        <v>105.377627056</v>
       </c>
       <c r="Q57">
-        <v>129.25329443</v>
+        <v>128.777627056</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1034790150948756</v>
+        <v>0.1045342180166789</v>
       </c>
       <c r="T57">
-        <v>1.056411417496072</v>
+        <v>1.075737829580858</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.046115959327341</v>
+        <v>4.956006745767924</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0661242559273387</v>
+        <v>0.06591320506198337</v>
       </c>
       <c r="C58">
-        <v>722.4233060541957</v>
+        <v>712.0069334949847</v>
       </c>
       <c r="D58">
-        <v>1319.182506054196</v>
+        <v>1321.999333494985</v>
       </c>
       <c r="E58">
-        <v>737.8392</v>
+        <v>751.0724</v>
       </c>
       <c r="F58">
-        <v>741.0592</v>
+        <v>754.2924</v>
       </c>
       <c r="G58">
         <v>144.3</v>
@@ -6043,28 +6043,28 @@
         <v>203.1</v>
       </c>
       <c r="M58">
-        <v>40.98057376000001</v>
+        <v>41.71236972000001</v>
       </c>
       <c r="N58">
-        <v>162.11942624</v>
+        <v>161.38763028</v>
       </c>
       <c r="O58">
-        <v>56.74179918399999</v>
+        <v>56.48567059799999</v>
       </c>
       <c r="P58">
-        <v>105.377627056</v>
+        <v>104.901959682</v>
       </c>
       <c r="Q58">
-        <v>128.777627056</v>
+        <v>128.301959682</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1045342180166789</v>
+        <v>0.1056385001441474</v>
       </c>
       <c r="T58">
-        <v>1.075737829580858</v>
+        <v>1.095963144553308</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.956006745767924</v>
+        <v>4.869059259000066</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06591320506198337</v>
+        <v>0.06570215419662805</v>
       </c>
       <c r="C59">
-        <v>712.0069334949847</v>
+        <v>701.6026161222004</v>
       </c>
       <c r="D59">
-        <v>1321.999333494985</v>
+        <v>1324.828216122201</v>
       </c>
       <c r="E59">
-        <v>751.0724</v>
+        <v>764.3056</v>
       </c>
       <c r="F59">
-        <v>754.2924</v>
+        <v>767.5256000000001</v>
       </c>
       <c r="G59">
         <v>144.3</v>
@@ -6125,28 +6125,28 @@
         <v>203.1</v>
       </c>
       <c r="M59">
-        <v>41.71236972000001</v>
+        <v>42.44416568</v>
       </c>
       <c r="N59">
-        <v>161.38763028</v>
+        <v>160.65583432</v>
       </c>
       <c r="O59">
-        <v>56.48567059799999</v>
+        <v>56.229542012</v>
       </c>
       <c r="P59">
-        <v>104.901959682</v>
+        <v>104.426292308</v>
       </c>
       <c r="Q59">
-        <v>128.301959682</v>
+        <v>127.826292308</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1056385001441474</v>
+        <v>0.1067953671348287</v>
       </c>
       <c r="T59">
-        <v>1.095963144553308</v>
+        <v>1.117151569762542</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.869059259000066</v>
+        <v>4.785109961431099</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06570215419662803</v>
+        <v>0.0654911033312727</v>
       </c>
       <c r="C60">
-        <v>701.6026161222007</v>
+        <v>691.2104314907368</v>
       </c>
       <c r="D60">
-        <v>1324.828216122201</v>
+        <v>1327.669231490737</v>
       </c>
       <c r="E60">
-        <v>764.3055999999999</v>
+        <v>777.5387999999999</v>
       </c>
       <c r="F60">
-        <v>767.5255999999999</v>
+        <v>780.7588</v>
       </c>
       <c r="G60">
         <v>144.3</v>
@@ -6207,28 +6207,28 @@
         <v>203.1</v>
       </c>
       <c r="M60">
-        <v>42.44416568</v>
+        <v>43.17596164</v>
       </c>
       <c r="N60">
-        <v>160.65583432</v>
+        <v>159.92403836</v>
       </c>
       <c r="O60">
-        <v>56.229542012</v>
+        <v>55.97341342599999</v>
       </c>
       <c r="P60">
-        <v>104.426292308</v>
+        <v>103.950624934</v>
       </c>
       <c r="Q60">
-        <v>127.826292308</v>
+        <v>127.350624934</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1067953671348287</v>
+        <v>0.1080086666616407</v>
       </c>
       <c r="T60">
-        <v>1.117151569762542</v>
+        <v>1.139373576689299</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.7851099614311</v>
+        <v>4.704006402762776</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0654911033312727</v>
+        <v>0.06528005246591737</v>
       </c>
       <c r="C61">
-        <v>691.2104314907368</v>
+        <v>680.8304578221621</v>
       </c>
       <c r="D61">
-        <v>1327.669231490737</v>
+        <v>1330.522457822162</v>
       </c>
       <c r="E61">
-        <v>777.5387999999999</v>
+        <v>790.7719999999999</v>
       </c>
       <c r="F61">
-        <v>780.7588</v>
+        <v>793.992</v>
       </c>
       <c r="G61">
         <v>144.3</v>
@@ -6289,28 +6289,28 @@
         <v>203.1</v>
       </c>
       <c r="M61">
-        <v>43.17596164</v>
+        <v>43.9077576</v>
       </c>
       <c r="N61">
-        <v>159.92403836</v>
+        <v>159.1922424</v>
       </c>
       <c r="O61">
-        <v>55.97341342599999</v>
+        <v>55.71728484</v>
       </c>
       <c r="P61">
-        <v>103.950624934</v>
+        <v>103.47495756</v>
       </c>
       <c r="Q61">
-        <v>127.350624934</v>
+        <v>126.87495756</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1080086666616407</v>
+        <v>0.1092826311647934</v>
       </c>
       <c r="T61">
-        <v>1.139373576689299</v>
+        <v>1.162706683962394</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.704006402762776</v>
+        <v>4.625606296050063</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06528005246591737</v>
+        <v>0.06506900160056205</v>
       </c>
       <c r="C62">
-        <v>680.8304578221621</v>
+        <v>670.4627740119018</v>
       </c>
       <c r="D62">
-        <v>1330.522457822162</v>
+        <v>1333.387974011902</v>
       </c>
       <c r="E62">
-        <v>790.7719999999999</v>
+        <v>804.0051999999999</v>
       </c>
       <c r="F62">
-        <v>793.992</v>
+        <v>807.2252</v>
       </c>
       <c r="G62">
         <v>144.3</v>
@@ -6371,28 +6371,28 @@
         <v>203.1</v>
       </c>
       <c r="M62">
-        <v>43.9077576</v>
+        <v>44.63955356</v>
       </c>
       <c r="N62">
-        <v>159.1922424</v>
+        <v>158.46044644</v>
       </c>
       <c r="O62">
-        <v>55.71728484</v>
+        <v>55.461156254</v>
       </c>
       <c r="P62">
-        <v>103.47495756</v>
+        <v>102.999290186</v>
       </c>
       <c r="Q62">
-        <v>126.87495756</v>
+        <v>126.399290186</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1092826311647934</v>
+        <v>0.1106219271809283</v>
       </c>
       <c r="T62">
-        <v>1.162706683962394</v>
+        <v>1.187236360839238</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.625606296050063</v>
+        <v>4.549776684639406</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06506900160056205</v>
+        <v>0.06586545073520672</v>
       </c>
       <c r="C63">
-        <v>670.4627740119018</v>
+        <v>646.4799646984052</v>
       </c>
       <c r="D63">
-        <v>1333.387974011902</v>
+        <v>1322.638364698405</v>
       </c>
       <c r="E63">
-        <v>804.0051999999999</v>
+        <v>817.2384</v>
       </c>
       <c r="F63">
-        <v>807.2252</v>
+        <v>820.4584</v>
       </c>
       <c r="G63">
         <v>144.3</v>
@@ -6453,45 +6453,45 @@
         <v>203.1</v>
       </c>
       <c r="M63">
-        <v>44.63955356</v>
+        <v>47.42249552000001</v>
       </c>
       <c r="N63">
-        <v>158.46044644</v>
+        <v>155.67750448</v>
       </c>
       <c r="O63">
-        <v>55.461156254</v>
+        <v>54.48712656799999</v>
       </c>
       <c r="P63">
-        <v>102.999290186</v>
+        <v>101.190377912</v>
       </c>
       <c r="Q63">
-        <v>126.399290186</v>
+        <v>124.590377912</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1106219271809283</v>
+        <v>0.1120317124610703</v>
       </c>
       <c r="T63">
-        <v>1.187236360839238</v>
+        <v>1.213057073341179</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.549776684639406</v>
+        <v>4.282777567332879</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06586545073520672</v>
+        <v>0.06567064986985138</v>
       </c>
       <c r="C64">
-        <v>646.4799646984052</v>
+        <v>635.8599325024107</v>
       </c>
       <c r="D64">
-        <v>1322.638364698405</v>
+        <v>1325.251532502411</v>
       </c>
       <c r="E64">
-        <v>817.2384</v>
+        <v>830.4716</v>
       </c>
       <c r="F64">
-        <v>820.4584</v>
+        <v>833.6916</v>
       </c>
       <c r="G64">
         <v>144.3</v>
@@ -6535,28 +6535,28 @@
         <v>203.1</v>
       </c>
       <c r="M64">
-        <v>47.42249552000001</v>
+        <v>48.18737448</v>
       </c>
       <c r="N64">
-        <v>155.67750448</v>
+        <v>154.91262552</v>
       </c>
       <c r="O64">
-        <v>54.48712656799999</v>
+        <v>54.219418932</v>
       </c>
       <c r="P64">
-        <v>101.190377912</v>
+        <v>100.693206588</v>
       </c>
       <c r="Q64">
-        <v>124.590377912</v>
+        <v>124.093206588</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1120317124610703</v>
+        <v>0.1135177023509497</v>
       </c>
       <c r="T64">
-        <v>1.213057073341179</v>
+        <v>1.240273500032414</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.282777567332879</v>
+        <v>4.214796971026009</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06567064986985138</v>
+        <v>0.06547584900449607</v>
       </c>
       <c r="C65">
-        <v>635.8599325024107</v>
+        <v>625.2502465422122</v>
       </c>
       <c r="D65">
-        <v>1325.251532502411</v>
+        <v>1327.875046542212</v>
       </c>
       <c r="E65">
-        <v>830.4716</v>
+        <v>843.7048</v>
       </c>
       <c r="F65">
-        <v>833.6916</v>
+        <v>846.9248</v>
       </c>
       <c r="G65">
         <v>144.3</v>
@@ -6617,28 +6617,28 @@
         <v>203.1</v>
       </c>
       <c r="M65">
-        <v>48.18737448</v>
+        <v>48.95225344000001</v>
       </c>
       <c r="N65">
-        <v>154.91262552</v>
+        <v>154.14774656</v>
       </c>
       <c r="O65">
-        <v>54.219418932</v>
+        <v>53.95171129599998</v>
       </c>
       <c r="P65">
-        <v>100.693206588</v>
+        <v>100.196035264</v>
       </c>
       <c r="Q65">
-        <v>124.093206588</v>
+        <v>123.596035264</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1135177023509497</v>
+        <v>0.1150862472347113</v>
       </c>
       <c r="T65">
-        <v>1.240273500032414</v>
+        <v>1.269001950428718</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.214796971026009</v>
+        <v>4.148940768353727</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06547584900449607</v>
+        <v>0.06528104813914073</v>
       </c>
       <c r="C66">
-        <v>625.2502465422122</v>
+        <v>614.6509683849953</v>
       </c>
       <c r="D66">
-        <v>1327.875046542212</v>
+        <v>1330.508968384995</v>
       </c>
       <c r="E66">
-        <v>843.7048</v>
+        <v>856.938</v>
       </c>
       <c r="F66">
-        <v>846.9248</v>
+        <v>860.158</v>
       </c>
       <c r="G66">
         <v>144.3</v>
@@ -6699,28 +6699,28 @@
         <v>203.1</v>
       </c>
       <c r="M66">
-        <v>48.95225344000001</v>
+        <v>49.7171324</v>
       </c>
       <c r="N66">
-        <v>154.14774656</v>
+        <v>153.3828676</v>
       </c>
       <c r="O66">
-        <v>53.95171129599998</v>
+        <v>53.68400365999999</v>
       </c>
       <c r="P66">
-        <v>100.196035264</v>
+        <v>99.69886394</v>
       </c>
       <c r="Q66">
-        <v>123.596035264</v>
+        <v>123.09886394</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1150862472347113</v>
+        <v>0.1167444232546878</v>
       </c>
       <c r="T66">
-        <v>1.269001950428718</v>
+        <v>1.299372026561953</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.148940768353727</v>
+        <v>4.085110910379054</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06528104813914073</v>
+        <v>0.0650862472737854</v>
       </c>
       <c r="C67">
-        <v>614.6509683849953</v>
+        <v>604.0621600874056</v>
       </c>
       <c r="D67">
-        <v>1330.508968384995</v>
+        <v>1333.153360087406</v>
       </c>
       <c r="E67">
-        <v>856.938</v>
+        <v>870.1712</v>
       </c>
       <c r="F67">
-        <v>860.158</v>
+        <v>873.3912</v>
       </c>
       <c r="G67">
         <v>144.3</v>
@@ -6781,28 +6781,28 @@
         <v>203.1</v>
       </c>
       <c r="M67">
-        <v>49.7171324</v>
+        <v>50.48201136000001</v>
       </c>
       <c r="N67">
-        <v>153.3828676</v>
+        <v>152.61798864</v>
       </c>
       <c r="O67">
-        <v>53.68400365999999</v>
+        <v>53.416296024</v>
       </c>
       <c r="P67">
-        <v>99.69886394</v>
+        <v>99.201692616</v>
       </c>
       <c r="Q67">
-        <v>123.09886394</v>
+        <v>122.601692616</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1167444232546878</v>
+        <v>0.1185001390405453</v>
       </c>
       <c r="T67">
-        <v>1.299372026561953</v>
+        <v>1.331528577761849</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.085110910379054</v>
+        <v>4.023215290524826</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0650862472737854</v>
+        <v>0.06641569640843006</v>
       </c>
       <c r="C68">
-        <v>604.0621600874056</v>
+        <v>572.9880196122125</v>
       </c>
       <c r="D68">
-        <v>1333.153360087406</v>
+        <v>1315.312419612213</v>
       </c>
       <c r="E68">
-        <v>870.1712</v>
+        <v>883.4044</v>
       </c>
       <c r="F68">
-        <v>873.3912</v>
+        <v>886.6244</v>
       </c>
       <c r="G68">
         <v>144.3</v>
@@ -6863,45 +6863,45 @@
         <v>203.1</v>
       </c>
       <c r="M68">
-        <v>50.48201136000001</v>
+        <v>54.35007572</v>
       </c>
       <c r="N68">
-        <v>152.61798864</v>
+        <v>148.74992428</v>
       </c>
       <c r="O68">
-        <v>53.416296024</v>
+        <v>52.062473498</v>
       </c>
       <c r="P68">
-        <v>99.201692616</v>
+        <v>96.68745078199998</v>
       </c>
       <c r="Q68">
-        <v>122.601692616</v>
+        <v>120.087450782</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1185001390405453</v>
+        <v>0.1203622618437275</v>
       </c>
       <c r="T68">
-        <v>1.331528577761849</v>
+        <v>1.365634010852648</v>
       </c>
       <c r="U68">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V68">
         <v>0.35</v>
       </c>
       <c r="W68">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.023215290524826</v>
+        <v>3.736885318179277</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06641569640843006</v>
+        <v>0.06624364554307474</v>
       </c>
       <c r="C69">
-        <v>572.9880196122125</v>
+        <v>562.0367610551605</v>
       </c>
       <c r="D69">
-        <v>1315.312419612213</v>
+        <v>1317.594361055161</v>
       </c>
       <c r="E69">
-        <v>883.4044</v>
+        <v>896.6376</v>
       </c>
       <c r="F69">
-        <v>886.6244</v>
+        <v>899.8576</v>
       </c>
       <c r="G69">
         <v>144.3</v>
@@ -6945,28 +6945,28 @@
         <v>203.1</v>
       </c>
       <c r="M69">
-        <v>54.35007572</v>
+        <v>55.16127088</v>
       </c>
       <c r="N69">
-        <v>148.74992428</v>
+        <v>147.93872912</v>
       </c>
       <c r="O69">
-        <v>52.062473498</v>
+        <v>51.778555192</v>
       </c>
       <c r="P69">
-        <v>96.68745078199998</v>
+        <v>96.16017392800001</v>
       </c>
       <c r="Q69">
-        <v>120.087450782</v>
+        <v>119.560173928</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1203622618437275</v>
+        <v>0.1223407673221086</v>
       </c>
       <c r="T69">
-        <v>1.365634010852648</v>
+        <v>1.401871033511622</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.736885318179277</v>
+        <v>3.681931122323699</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06624364554307474</v>
+        <v>0.06607159467771941</v>
       </c>
       <c r="C70">
-        <v>562.0367610551605</v>
+        <v>551.0934341597657</v>
       </c>
       <c r="D70">
-        <v>1317.594361055161</v>
+        <v>1319.884234159766</v>
       </c>
       <c r="E70">
-        <v>896.6376</v>
+        <v>909.8708</v>
       </c>
       <c r="F70">
-        <v>899.8576</v>
+        <v>913.0908000000001</v>
       </c>
       <c r="G70">
         <v>144.3</v>
@@ -7027,28 +7027,28 @@
         <v>203.1</v>
       </c>
       <c r="M70">
-        <v>55.16127088</v>
+        <v>55.97246604</v>
       </c>
       <c r="N70">
-        <v>147.93872912</v>
+        <v>147.12753396</v>
       </c>
       <c r="O70">
-        <v>51.778555192</v>
+        <v>51.494636886</v>
       </c>
       <c r="P70">
-        <v>96.16017392800001</v>
+        <v>95.632897074</v>
       </c>
       <c r="Q70">
-        <v>119.560173928</v>
+        <v>119.032897074</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1223407673221086</v>
+        <v>0.1244469183152239</v>
       </c>
       <c r="T70">
-        <v>1.401871033511622</v>
+        <v>1.440445928600206</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.681931122323699</v>
+        <v>3.628569801710313</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06607159467771941</v>
+        <v>0.06589954381236407</v>
       </c>
       <c r="C71">
-        <v>551.0934341597657</v>
+        <v>540.1580803517936</v>
       </c>
       <c r="D71">
-        <v>1319.884234159766</v>
+        <v>1322.182080351794</v>
       </c>
       <c r="E71">
-        <v>909.8708</v>
+        <v>923.104</v>
       </c>
       <c r="F71">
-        <v>913.0908000000001</v>
+        <v>926.3240000000001</v>
       </c>
       <c r="G71">
         <v>144.3</v>
@@ -7109,28 +7109,28 @@
         <v>203.1</v>
       </c>
       <c r="M71">
-        <v>55.97246604</v>
+        <v>56.7836612</v>
       </c>
       <c r="N71">
-        <v>147.12753396</v>
+        <v>146.3163388</v>
       </c>
       <c r="O71">
-        <v>51.494636886</v>
+        <v>51.21071857999999</v>
       </c>
       <c r="P71">
-        <v>95.632897074</v>
+        <v>95.10562021999999</v>
       </c>
       <c r="Q71">
-        <v>119.032897074</v>
+        <v>118.50562022</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1244469183152239</v>
+        <v>0.1266934793745469</v>
       </c>
       <c r="T71">
-        <v>1.440445928600206</v>
+        <v>1.481592483361364</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.628569801710313</v>
+        <v>3.576733090257307</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06589954381236407</v>
+        <v>0.06572749294700875</v>
       </c>
       <c r="C72">
-        <v>540.1580803517936</v>
+        <v>529.2307413459938</v>
       </c>
       <c r="D72">
-        <v>1322.182080351794</v>
+        <v>1324.487941345994</v>
       </c>
       <c r="E72">
-        <v>923.104</v>
+        <v>936.3372000000001</v>
       </c>
       <c r="F72">
-        <v>926.3240000000001</v>
+        <v>939.5572000000001</v>
       </c>
       <c r="G72">
         <v>144.3</v>
@@ -7191,28 +7191,28 @@
         <v>203.1</v>
       </c>
       <c r="M72">
-        <v>56.7836612</v>
+        <v>57.59485636000001</v>
       </c>
       <c r="N72">
-        <v>146.3163388</v>
+        <v>145.50514364</v>
       </c>
       <c r="O72">
-        <v>51.21071857999999</v>
+        <v>50.92680027399999</v>
       </c>
       <c r="P72">
-        <v>95.10562021999999</v>
+        <v>94.57834336599998</v>
       </c>
       <c r="Q72">
-        <v>118.50562022</v>
+        <v>117.978343366</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1266934793745469</v>
+        <v>0.1290949756793405</v>
       </c>
       <c r="T72">
-        <v>1.481592483361364</v>
+        <v>1.525576731554325</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.576733090257307</v>
+        <v>3.526356567859317</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06572749294700875</v>
+        <v>0.06686584208165343</v>
       </c>
       <c r="C73">
-        <v>529.230741345994</v>
+        <v>500.8888815848211</v>
       </c>
       <c r="D73">
-        <v>1324.487941345994</v>
+        <v>1309.379281584821</v>
       </c>
       <c r="E73">
-        <v>936.3371999999998</v>
+        <v>949.5703999999998</v>
       </c>
       <c r="F73">
-        <v>939.5571999999999</v>
+        <v>952.7903999999999</v>
       </c>
       <c r="G73">
         <v>144.3</v>
@@ -7273,45 +7273,45 @@
         <v>203.1</v>
       </c>
       <c r="M73">
-        <v>57.59485635999999</v>
+        <v>61.07386464</v>
       </c>
       <c r="N73">
-        <v>145.50514364</v>
+        <v>142.02613536</v>
       </c>
       <c r="O73">
-        <v>50.92680027399999</v>
+        <v>49.709147376</v>
       </c>
       <c r="P73">
-        <v>94.57834336600001</v>
+        <v>92.31698798400001</v>
       </c>
       <c r="Q73">
-        <v>117.978343366</v>
+        <v>115.716987984</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1290949756793405</v>
+        <v>0.1316680074344765</v>
       </c>
       <c r="T73">
-        <v>1.525576731554324</v>
+        <v>1.572702711761069</v>
       </c>
       <c r="U73">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.35</v>
       </c>
       <c r="W73">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.526356567859318</v>
+        <v>3.32548138548581</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06686584208165343</v>
+        <v>0.06671199121629809</v>
       </c>
       <c r="C74">
-        <v>500.8888815848211</v>
+        <v>489.677480370119</v>
       </c>
       <c r="D74">
-        <v>1309.379281584821</v>
+        <v>1311.401080370119</v>
       </c>
       <c r="E74">
-        <v>949.5703999999998</v>
+        <v>962.8035999999998</v>
       </c>
       <c r="F74">
-        <v>952.7903999999999</v>
+        <v>966.0235999999999</v>
       </c>
       <c r="G74">
         <v>144.3</v>
@@ -7355,28 +7355,28 @@
         <v>203.1</v>
       </c>
       <c r="M74">
-        <v>61.07386464</v>
+        <v>61.92211276</v>
       </c>
       <c r="N74">
-        <v>142.02613536</v>
+        <v>141.17788724</v>
       </c>
       <c r="O74">
-        <v>49.709147376</v>
+        <v>49.41226053399999</v>
       </c>
       <c r="P74">
-        <v>92.31698798400001</v>
+        <v>91.76562670600001</v>
       </c>
       <c r="Q74">
-        <v>115.716987984</v>
+        <v>115.165626706</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1316680074344765</v>
+        <v>0.1344316341344373</v>
       </c>
       <c r="T74">
-        <v>1.572702711761069</v>
+        <v>1.62331950531646</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.32548138548581</v>
+        <v>3.279926845958607</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06671199121629809</v>
+        <v>0.06655814035094276</v>
       </c>
       <c r="C75">
-        <v>489.677480370119</v>
+        <v>478.4723324876265</v>
       </c>
       <c r="D75">
-        <v>1311.401080370119</v>
+        <v>1313.429132487626</v>
       </c>
       <c r="E75">
-        <v>962.8035999999998</v>
+        <v>976.0367999999999</v>
       </c>
       <c r="F75">
-        <v>966.0235999999999</v>
+        <v>979.2567999999999</v>
       </c>
       <c r="G75">
         <v>144.3</v>
@@ -7437,28 +7437,28 @@
         <v>203.1</v>
       </c>
       <c r="M75">
-        <v>61.92211276</v>
+        <v>62.77036088</v>
       </c>
       <c r="N75">
-        <v>141.17788724</v>
+        <v>140.32963912</v>
       </c>
       <c r="O75">
-        <v>49.41226053399999</v>
+        <v>49.115373692</v>
       </c>
       <c r="P75">
-        <v>91.76562670600001</v>
+        <v>91.214265428</v>
       </c>
       <c r="Q75">
-        <v>115.165626706</v>
+        <v>114.614265428</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1344316341344373</v>
+        <v>0.137407847503626</v>
       </c>
       <c r="T75">
-        <v>1.62331950531646</v>
+        <v>1.677829898376113</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.279926845958607</v>
+        <v>3.235603510202409</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06655814035094276</v>
+        <v>0.06640428948558744</v>
       </c>
       <c r="C76">
-        <v>478.4723324876265</v>
+        <v>467.2734669941899</v>
       </c>
       <c r="D76">
-        <v>1313.429132487626</v>
+        <v>1315.46346699419</v>
       </c>
       <c r="E76">
-        <v>976.0367999999999</v>
+        <v>989.27</v>
       </c>
       <c r="F76">
-        <v>979.2567999999999</v>
+        <v>992.49</v>
       </c>
       <c r="G76">
         <v>144.3</v>
@@ -7519,28 +7519,28 @@
         <v>203.1</v>
       </c>
       <c r="M76">
-        <v>62.77036088</v>
+        <v>63.61860900000001</v>
       </c>
       <c r="N76">
-        <v>140.32963912</v>
+        <v>139.481391</v>
       </c>
       <c r="O76">
-        <v>49.115373692</v>
+        <v>48.81848684999999</v>
       </c>
       <c r="P76">
-        <v>91.214265428</v>
+        <v>90.66290414999999</v>
       </c>
       <c r="Q76">
-        <v>114.614265428</v>
+        <v>114.06290415</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.137407847503626</v>
+        <v>0.1406221579423497</v>
       </c>
       <c r="T76">
-        <v>1.677829898376113</v>
+        <v>1.736701122880539</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.235603510202409</v>
+        <v>3.192462130066377</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06640428948558744</v>
+        <v>0.0662504386202321</v>
       </c>
       <c r="C77">
-        <v>467.2734669941899</v>
+        <v>456.080913126956</v>
       </c>
       <c r="D77">
-        <v>1315.46346699419</v>
+        <v>1317.504113126956</v>
       </c>
       <c r="E77">
-        <v>989.27</v>
+        <v>1002.5032</v>
       </c>
       <c r="F77">
-        <v>992.49</v>
+        <v>1005.7232</v>
       </c>
       <c r="G77">
         <v>144.3</v>
@@ -7601,28 +7601,28 @@
         <v>203.1</v>
       </c>
       <c r="M77">
-        <v>63.61860900000001</v>
+        <v>64.46685712</v>
       </c>
       <c r="N77">
-        <v>139.481391</v>
+        <v>138.63314288</v>
       </c>
       <c r="O77">
-        <v>48.81848684999999</v>
+        <v>48.52160000799999</v>
       </c>
       <c r="P77">
-        <v>90.66290414999999</v>
+        <v>90.11154287199999</v>
       </c>
       <c r="Q77">
-        <v>114.06290415</v>
+        <v>113.511542872</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1406221579423497</v>
+        <v>0.1441043275843004</v>
       </c>
       <c r="T77">
-        <v>1.736701122880539</v>
+        <v>1.800478282760333</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.192462130066377</v>
+        <v>3.150456049407609</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0662504386202321</v>
+        <v>0.06609658775487677</v>
       </c>
       <c r="C78">
-        <v>456.080913126956</v>
+        <v>444.8947003047736</v>
       </c>
       <c r="D78">
-        <v>1317.504113126956</v>
+        <v>1319.551100304774</v>
       </c>
       <c r="E78">
-        <v>1002.5032</v>
+        <v>1015.7364</v>
       </c>
       <c r="F78">
-        <v>1005.7232</v>
+        <v>1018.9564</v>
       </c>
       <c r="G78">
         <v>144.3</v>
@@ -7683,28 +7683,28 @@
         <v>203.1</v>
       </c>
       <c r="M78">
-        <v>64.46685712</v>
+        <v>65.31510524000001</v>
       </c>
       <c r="N78">
-        <v>138.63314288</v>
+        <v>137.78489476</v>
       </c>
       <c r="O78">
-        <v>48.52160000799999</v>
+        <v>48.22471316599999</v>
       </c>
       <c r="P78">
-        <v>90.11154287199999</v>
+        <v>89.560181594</v>
       </c>
       <c r="Q78">
-        <v>113.511542872</v>
+        <v>112.960181594</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1441043275843004</v>
+        <v>0.1478892945864207</v>
       </c>
       <c r="T78">
-        <v>1.800478282760333</v>
+        <v>1.869801282629673</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.150456049407609</v>
+        <v>3.109541035778939</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06609658775487677</v>
+        <v>0.06594273688952143</v>
       </c>
       <c r="C79">
-        <v>444.8947003047736</v>
+        <v>433.7148581296055</v>
       </c>
       <c r="D79">
-        <v>1319.551100304774</v>
+        <v>1321.604458129606</v>
       </c>
       <c r="E79">
-        <v>1015.7364</v>
+        <v>1028.9696</v>
       </c>
       <c r="F79">
-        <v>1018.9564</v>
+        <v>1032.1896</v>
       </c>
       <c r="G79">
         <v>144.3</v>
@@ -7765,28 +7765,28 @@
         <v>203.1</v>
       </c>
       <c r="M79">
-        <v>65.31510524000001</v>
+        <v>66.16335336</v>
       </c>
       <c r="N79">
-        <v>137.78489476</v>
+        <v>136.93664664</v>
       </c>
       <c r="O79">
-        <v>48.22471316599999</v>
+        <v>47.92782632399999</v>
       </c>
       <c r="P79">
-        <v>89.560181594</v>
+        <v>89.008820316</v>
       </c>
       <c r="Q79">
-        <v>112.960181594</v>
+        <v>112.408820316</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1478892945864207</v>
+        <v>0.1520183494978247</v>
       </c>
       <c r="T79">
-        <v>1.869801282629673</v>
+        <v>1.945426373396227</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.109541035778939</v>
+        <v>3.069675125063824</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06594273688952143</v>
+        <v>0.0657888860241661</v>
       </c>
       <c r="C80">
-        <v>433.7148581296055</v>
+        <v>422.5414163879575</v>
       </c>
       <c r="D80">
-        <v>1321.604458129606</v>
+        <v>1323.664216387958</v>
       </c>
       <c r="E80">
-        <v>1028.9696</v>
+        <v>1042.2028</v>
       </c>
       <c r="F80">
-        <v>1032.1896</v>
+        <v>1045.4228</v>
       </c>
       <c r="G80">
         <v>144.3</v>
@@ -7847,28 +7847,28 @@
         <v>203.1</v>
       </c>
       <c r="M80">
-        <v>66.16335336</v>
+        <v>67.01160148000001</v>
       </c>
       <c r="N80">
-        <v>136.93664664</v>
+        <v>136.08839852</v>
       </c>
       <c r="O80">
-        <v>47.92782632399999</v>
+        <v>47.630939482</v>
       </c>
       <c r="P80">
-        <v>89.008820316</v>
+        <v>88.457459038</v>
       </c>
       <c r="Q80">
-        <v>112.408820316</v>
+        <v>111.857459038</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1520183494978247</v>
+        <v>0.1565406477341243</v>
       </c>
       <c r="T80">
-        <v>1.945426373396227</v>
+        <v>2.028253853759596</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.069675125063824</v>
+        <v>3.030818477911117</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0657888860241661</v>
+        <v>0.06969103515881078</v>
       </c>
       <c r="C81">
-        <v>422.5414163879575</v>
+        <v>358.9744083430205</v>
       </c>
       <c r="D81">
-        <v>1323.664216387958</v>
+        <v>1273.330408343021</v>
       </c>
       <c r="E81">
-        <v>1042.2028</v>
+        <v>1055.436</v>
       </c>
       <c r="F81">
-        <v>1045.4228</v>
+        <v>1058.656</v>
       </c>
       <c r="G81">
         <v>144.3</v>
@@ -7929,45 +7929,45 @@
         <v>203.1</v>
       </c>
       <c r="M81">
-        <v>67.01160148000001</v>
+        <v>76.11736640000001</v>
       </c>
       <c r="N81">
-        <v>136.08839852</v>
+        <v>126.9826336</v>
       </c>
       <c r="O81">
-        <v>47.630939482</v>
+        <v>44.44392175999999</v>
       </c>
       <c r="P81">
-        <v>88.457459038</v>
+        <v>82.53871183999999</v>
       </c>
       <c r="Q81">
-        <v>111.857459038</v>
+        <v>105.93871184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1565406477341243</v>
+        <v>0.1615151757940539</v>
       </c>
       <c r="T81">
-        <v>2.028253853759596</v>
+        <v>2.119364082159302</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.35</v>
       </c>
       <c r="W81">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.030818477911117</v>
+        <v>2.668247859925957</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06969103515881078</v>
+        <v>0.06958788429345544</v>
       </c>
       <c r="C82">
-        <v>358.9744083430205</v>
+        <v>347.0224435195132</v>
       </c>
       <c r="D82">
-        <v>1273.330408343021</v>
+        <v>1274.611643519513</v>
       </c>
       <c r="E82">
-        <v>1055.436</v>
+        <v>1068.6692</v>
       </c>
       <c r="F82">
-        <v>1058.656</v>
+        <v>1071.8892</v>
       </c>
       <c r="G82">
         <v>144.3</v>
@@ -8011,28 +8011,28 @@
         <v>203.1</v>
       </c>
       <c r="M82">
-        <v>76.11736640000001</v>
+        <v>77.06883348000001</v>
       </c>
       <c r="N82">
-        <v>126.9826336</v>
+        <v>126.03116652</v>
       </c>
       <c r="O82">
-        <v>44.44392175999999</v>
+        <v>44.11090828199999</v>
       </c>
       <c r="P82">
-        <v>82.53871183999999</v>
+        <v>81.920258238</v>
       </c>
       <c r="Q82">
-        <v>105.93871184</v>
+        <v>105.320258238</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1615151757940539</v>
+        <v>0.1670133383866076</v>
       </c>
       <c r="T82">
-        <v>2.119364082159302</v>
+        <v>2.220064860916871</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.668247859925957</v>
+        <v>2.635306528321933</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06958788429345544</v>
+        <v>0.06948473342810012</v>
       </c>
       <c r="C83">
-        <v>347.0224435195132</v>
+        <v>335.0730596710378</v>
       </c>
       <c r="D83">
-        <v>1274.611643519513</v>
+        <v>1275.895459671038</v>
       </c>
       <c r="E83">
-        <v>1068.6692</v>
+        <v>1081.9024</v>
       </c>
       <c r="F83">
-        <v>1071.8892</v>
+        <v>1085.1224</v>
       </c>
       <c r="G83">
         <v>144.3</v>
@@ -8093,28 +8093,28 @@
         <v>203.1</v>
       </c>
       <c r="M83">
-        <v>77.06883348000001</v>
+        <v>78.02030056000001</v>
       </c>
       <c r="N83">
-        <v>126.03116652</v>
+        <v>125.07969944</v>
       </c>
       <c r="O83">
-        <v>44.11090828199999</v>
+        <v>43.77789480399999</v>
       </c>
       <c r="P83">
-        <v>81.920258238</v>
+        <v>81.30180463599999</v>
       </c>
       <c r="Q83">
-        <v>105.320258238</v>
+        <v>104.701804636</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1670133383866076</v>
+        <v>0.1731224079338896</v>
       </c>
       <c r="T83">
-        <v>2.220064860916871</v>
+        <v>2.331954615091948</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.635306528321933</v>
+        <v>2.603168643830202</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06948473342810012</v>
+        <v>0.06938158256274479</v>
       </c>
       <c r="C84">
-        <v>335.0730596710378</v>
+        <v>323.1262646042969</v>
       </c>
       <c r="D84">
-        <v>1275.895459671038</v>
+        <v>1277.181864604297</v>
       </c>
       <c r="E84">
-        <v>1081.9024</v>
+        <v>1095.1356</v>
       </c>
       <c r="F84">
-        <v>1085.1224</v>
+        <v>1098.3556</v>
       </c>
       <c r="G84">
         <v>144.3</v>
@@ -8175,28 +8175,28 @@
         <v>203.1</v>
       </c>
       <c r="M84">
-        <v>78.02030056000001</v>
+        <v>78.97176764000001</v>
       </c>
       <c r="N84">
-        <v>125.07969944</v>
+        <v>124.12823236</v>
       </c>
       <c r="O84">
-        <v>43.77789480399999</v>
+        <v>43.44488132599999</v>
       </c>
       <c r="P84">
-        <v>81.30180463599999</v>
+        <v>80.683351034</v>
       </c>
       <c r="Q84">
-        <v>104.701804636</v>
+        <v>104.083351034</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1731224079338896</v>
+        <v>0.1799501915455576</v>
       </c>
       <c r="T84">
-        <v>2.331954615091948</v>
+        <v>2.457007869758211</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.603168643830202</v>
+        <v>2.571805166193694</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06938158256274479</v>
+        <v>0.06927843169738945</v>
       </c>
       <c r="C85">
-        <v>323.1262646042969</v>
+        <v>311.18206615751</v>
       </c>
       <c r="D85">
-        <v>1277.181864604297</v>
+        <v>1278.47086615751</v>
       </c>
       <c r="E85">
-        <v>1095.1356</v>
+        <v>1108.3688</v>
       </c>
       <c r="F85">
-        <v>1098.3556</v>
+        <v>1111.5888</v>
       </c>
       <c r="G85">
         <v>144.3</v>
@@ -8257,28 +8257,28 @@
         <v>203.1</v>
       </c>
       <c r="M85">
-        <v>78.97176764000001</v>
+        <v>79.92323472000001</v>
       </c>
       <c r="N85">
-        <v>124.12823236</v>
+        <v>123.17676528</v>
       </c>
       <c r="O85">
-        <v>43.44488132599999</v>
+        <v>43.11186784799999</v>
       </c>
       <c r="P85">
-        <v>80.683351034</v>
+        <v>80.064897432</v>
       </c>
       <c r="Q85">
-        <v>104.083351034</v>
+        <v>103.464897432</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1799501915455576</v>
+        <v>0.1876314481086842</v>
       </c>
       <c r="T85">
-        <v>2.457007869758211</v>
+        <v>2.597692781257756</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.571805166193694</v>
+        <v>2.541188438024721</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06927843169738945</v>
+        <v>0.06917528083203413</v>
       </c>
       <c r="C86">
-        <v>311.18206615751</v>
+        <v>299.2404722005704</v>
       </c>
       <c r="D86">
-        <v>1278.47086615751</v>
+        <v>1279.76247220057</v>
       </c>
       <c r="E86">
-        <v>1108.3688</v>
+        <v>1121.602</v>
       </c>
       <c r="F86">
-        <v>1111.5888</v>
+        <v>1124.822</v>
       </c>
       <c r="G86">
         <v>144.3</v>
@@ -8339,28 +8339,28 @@
         <v>203.1</v>
       </c>
       <c r="M86">
-        <v>79.92323472000001</v>
+        <v>80.8747018</v>
       </c>
       <c r="N86">
-        <v>123.17676528</v>
+        <v>122.2252982</v>
       </c>
       <c r="O86">
-        <v>43.11186784799999</v>
+        <v>42.77885437</v>
       </c>
       <c r="P86">
-        <v>80.064897432</v>
+        <v>79.44644382999999</v>
       </c>
       <c r="Q86">
-        <v>103.464897432</v>
+        <v>102.84644383</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1876314481086841</v>
+        <v>0.1963368722135608</v>
       </c>
       <c r="T86">
-        <v>2.597692781257754</v>
+        <v>2.757135680957239</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.541188438024721</v>
+        <v>2.511292103459725</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06917528083203413</v>
+        <v>0.07125222996667881</v>
       </c>
       <c r="C87">
-        <v>299.2404722005704</v>
+        <v>260.4934307136555</v>
       </c>
       <c r="D87">
-        <v>1279.76247220057</v>
+        <v>1254.248630713656</v>
       </c>
       <c r="E87">
-        <v>1121.602</v>
+        <v>1134.8352</v>
       </c>
       <c r="F87">
-        <v>1124.822</v>
+        <v>1138.0552</v>
       </c>
       <c r="G87">
         <v>144.3</v>
@@ -8421,45 +8421,45 @@
         <v>203.1</v>
       </c>
       <c r="M87">
-        <v>80.8747018</v>
+        <v>86.26458416000001</v>
       </c>
       <c r="N87">
-        <v>122.2252982</v>
+        <v>116.83541584</v>
       </c>
       <c r="O87">
-        <v>42.77885437</v>
+        <v>40.89239554399999</v>
       </c>
       <c r="P87">
-        <v>79.44644382999999</v>
+        <v>75.94302029599999</v>
       </c>
       <c r="Q87">
-        <v>102.84644383</v>
+        <v>99.34302029599999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1963368722135608</v>
+        <v>0.20628592833342</v>
       </c>
       <c r="T87">
-        <v>2.757135680957239</v>
+        <v>2.93935613775665</v>
       </c>
       <c r="U87">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
         <v>0.35</v>
       </c>
       <c r="W87">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.511292103459725</v>
+        <v>2.354384501793905</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07125222996667881</v>
+        <v>0.07117442910132346</v>
       </c>
       <c r="C88">
-        <v>260.4934307136555</v>
+        <v>248.1976052193475</v>
       </c>
       <c r="D88">
-        <v>1254.248630713656</v>
+        <v>1255.186005219347</v>
       </c>
       <c r="E88">
-        <v>1134.8352</v>
+        <v>1148.0684</v>
       </c>
       <c r="F88">
-        <v>1138.0552</v>
+        <v>1151.2884</v>
       </c>
       <c r="G88">
         <v>144.3</v>
@@ -8503,28 +8503,28 @@
         <v>203.1</v>
       </c>
       <c r="M88">
-        <v>86.26458416000001</v>
+        <v>87.26766071999999</v>
       </c>
       <c r="N88">
-        <v>116.83541584</v>
+        <v>115.83233928</v>
       </c>
       <c r="O88">
-        <v>40.89239554399999</v>
+        <v>40.54131874799999</v>
       </c>
       <c r="P88">
-        <v>75.94302029599999</v>
+        <v>75.291020532</v>
       </c>
       <c r="Q88">
-        <v>99.34302029599999</v>
+        <v>98.69102053200001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.20628592833342</v>
+        <v>0.2177656084717189</v>
       </c>
       <c r="T88">
-        <v>2.93935613775665</v>
+        <v>3.149610510986739</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.354384501793905</v>
+        <v>2.327322610968688</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07117442910132346</v>
+        <v>0.07109662823596814</v>
       </c>
       <c r="C89">
-        <v>248.1976052193475</v>
+        <v>235.9031818842543</v>
       </c>
       <c r="D89">
-        <v>1255.186005219347</v>
+        <v>1256.124781884254</v>
       </c>
       <c r="E89">
-        <v>1148.0684</v>
+        <v>1161.3016</v>
       </c>
       <c r="F89">
-        <v>1151.2884</v>
+        <v>1164.5216</v>
       </c>
       <c r="G89">
         <v>144.3</v>
@@ -8585,28 +8585,28 @@
         <v>203.1</v>
       </c>
       <c r="M89">
-        <v>87.26766071999999</v>
+        <v>88.27073728000001</v>
       </c>
       <c r="N89">
-        <v>115.83233928</v>
+        <v>114.82926272</v>
       </c>
       <c r="O89">
-        <v>40.54131874799999</v>
+        <v>40.19024195199999</v>
       </c>
       <c r="P89">
-        <v>75.291020532</v>
+        <v>74.63902076799999</v>
       </c>
       <c r="Q89">
-        <v>98.69102053200001</v>
+        <v>98.039020768</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2177656084717189</v>
+        <v>0.2311585686330678</v>
       </c>
       <c r="T89">
-        <v>3.149610510986739</v>
+        <v>3.394907279755178</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.327322610968688</v>
+        <v>2.300875763116771</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07109662823596814</v>
+        <v>0.07101882737061281</v>
       </c>
       <c r="C90">
-        <v>235.9031818842543</v>
+        <v>223.6101638568339</v>
       </c>
       <c r="D90">
-        <v>1256.124781884254</v>
+        <v>1257.064963856834</v>
       </c>
       <c r="E90">
-        <v>1161.3016</v>
+        <v>1174.5348</v>
       </c>
       <c r="F90">
-        <v>1164.5216</v>
+        <v>1177.7548</v>
       </c>
       <c r="G90">
         <v>144.3</v>
@@ -8667,28 +8667,28 @@
         <v>203.1</v>
       </c>
       <c r="M90">
-        <v>88.27073728000001</v>
+        <v>89.27381384</v>
       </c>
       <c r="N90">
-        <v>114.82926272</v>
+        <v>113.82618616</v>
       </c>
       <c r="O90">
-        <v>40.19024195199999</v>
+        <v>39.83916515599999</v>
       </c>
       <c r="P90">
-        <v>74.63902076799999</v>
+        <v>73.987021004</v>
       </c>
       <c r="Q90">
-        <v>98.039020768</v>
+        <v>97.38702100399999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2311585686330678</v>
+        <v>0.2469866124601164</v>
       </c>
       <c r="T90">
-        <v>3.394907279755178</v>
+        <v>3.684803461026967</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.300875763116771</v>
+        <v>2.275023226452538</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07101882737061281</v>
+        <v>0.07094102650525747</v>
       </c>
       <c r="C91">
-        <v>223.6101638568339</v>
+        <v>211.3185542949757</v>
       </c>
       <c r="D91">
-        <v>1257.064963856834</v>
+        <v>1258.006554294976</v>
       </c>
       <c r="E91">
-        <v>1174.5348</v>
+        <v>1187.768</v>
       </c>
       <c r="F91">
-        <v>1177.7548</v>
+        <v>1190.988</v>
       </c>
       <c r="G91">
         <v>144.3</v>
@@ -8749,28 +8749,28 @@
         <v>203.1</v>
       </c>
       <c r="M91">
-        <v>89.27381384</v>
+        <v>90.27689040000001</v>
       </c>
       <c r="N91">
-        <v>113.82618616</v>
+        <v>112.8231096</v>
       </c>
       <c r="O91">
-        <v>39.83916515599999</v>
+        <v>39.48808835999999</v>
       </c>
       <c r="P91">
-        <v>73.987021004</v>
+        <v>73.33502123999999</v>
       </c>
       <c r="Q91">
-        <v>97.38702100399999</v>
+        <v>96.73502123999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2469866124601164</v>
+        <v>0.2659802650525747</v>
       </c>
       <c r="T91">
-        <v>3.684803461026967</v>
+        <v>4.032678878553115</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.275023226452538</v>
+        <v>2.249745190603065</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07094102650525747</v>
+        <v>0.07086322563990215</v>
       </c>
       <c r="C92">
-        <v>211.3185542949757</v>
+        <v>199.0283563660382</v>
       </c>
       <c r="D92">
-        <v>1258.006554294976</v>
+        <v>1258.949556366038</v>
       </c>
       <c r="E92">
-        <v>1187.768</v>
+        <v>1201.0012</v>
       </c>
       <c r="F92">
-        <v>1190.988</v>
+        <v>1204.2212</v>
       </c>
       <c r="G92">
         <v>144.3</v>
@@ -8831,28 +8831,28 @@
         <v>203.1</v>
       </c>
       <c r="M92">
-        <v>90.27689040000001</v>
+        <v>91.27996696000001</v>
       </c>
       <c r="N92">
-        <v>112.8231096</v>
+        <v>111.82003304</v>
       </c>
       <c r="O92">
-        <v>39.48808835999999</v>
+        <v>39.13701156399999</v>
       </c>
       <c r="P92">
-        <v>73.33502123999999</v>
+        <v>72.68302147599999</v>
       </c>
       <c r="Q92">
-        <v>96.73502123999998</v>
+        <v>96.083021476</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2659802650525747</v>
+        <v>0.2891947293322461</v>
       </c>
       <c r="T92">
-        <v>4.032678878553115</v>
+        <v>4.457859944418408</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.249745190603065</v>
+        <v>2.225022715981053</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07086322563990215</v>
+        <v>0.07078542477454683</v>
       </c>
       <c r="C93">
-        <v>199.0283563660382</v>
+        <v>186.7395732468835</v>
       </c>
       <c r="D93">
-        <v>1258.949556366038</v>
+        <v>1259.893973246884</v>
       </c>
       <c r="E93">
-        <v>1201.0012</v>
+        <v>1214.2344</v>
       </c>
       <c r="F93">
-        <v>1204.2212</v>
+        <v>1217.4544</v>
       </c>
       <c r="G93">
         <v>144.3</v>
@@ -8913,28 +8913,28 @@
         <v>203.1</v>
       </c>
       <c r="M93">
-        <v>91.27996696000001</v>
+        <v>92.28304352000001</v>
       </c>
       <c r="N93">
-        <v>111.82003304</v>
+        <v>110.81695648</v>
       </c>
       <c r="O93">
-        <v>39.13701156399999</v>
+        <v>38.78593476799999</v>
       </c>
       <c r="P93">
-        <v>72.68302147599999</v>
+        <v>72.031021712</v>
       </c>
       <c r="Q93">
-        <v>96.083021476</v>
+        <v>95.43102171199999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2891947293322461</v>
+        <v>0.3182128096818353</v>
       </c>
       <c r="T93">
-        <v>4.457859944418408</v>
+        <v>4.989336276750024</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.225022715981053</v>
+        <v>2.20083768645952</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07078542477454683</v>
+        <v>0.0707076239091915</v>
       </c>
       <c r="C94">
-        <v>186.7395732468835</v>
+        <v>174.4522081239154</v>
       </c>
       <c r="D94">
-        <v>1259.893973246884</v>
+        <v>1260.839808123915</v>
       </c>
       <c r="E94">
-        <v>1214.2344</v>
+        <v>1227.4676</v>
       </c>
       <c r="F94">
-        <v>1217.4544</v>
+        <v>1230.6876</v>
       </c>
       <c r="G94">
         <v>144.3</v>
@@ -8995,28 +8995,28 @@
         <v>203.1</v>
       </c>
       <c r="M94">
-        <v>92.28304352000001</v>
+        <v>93.28612008</v>
       </c>
       <c r="N94">
-        <v>110.81695648</v>
+        <v>109.81387992</v>
       </c>
       <c r="O94">
-        <v>38.78593476799999</v>
+        <v>38.434857972</v>
       </c>
       <c r="P94">
-        <v>72.031021712</v>
+        <v>71.379021948</v>
       </c>
       <c r="Q94">
-        <v>95.43102171199999</v>
+        <v>94.77902194800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3182128096818353</v>
+        <v>0.3555217701313071</v>
       </c>
       <c r="T94">
-        <v>4.989336276750024</v>
+        <v>5.672662989747816</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.20083768645952</v>
+        <v>2.17717276509974</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0707076239091915</v>
+        <v>0.07062982304383617</v>
       </c>
       <c r="C95">
-        <v>174.4522081239154</v>
+        <v>162.1662641931109</v>
       </c>
       <c r="D95">
-        <v>1260.839808123915</v>
+        <v>1261.787064193111</v>
       </c>
       <c r="E95">
-        <v>1227.4676</v>
+        <v>1240.7008</v>
       </c>
       <c r="F95">
-        <v>1230.6876</v>
+        <v>1243.9208</v>
       </c>
       <c r="G95">
         <v>144.3</v>
@@ -9077,28 +9077,28 @@
         <v>203.1</v>
       </c>
       <c r="M95">
-        <v>93.28612008</v>
+        <v>94.28919664000001</v>
       </c>
       <c r="N95">
-        <v>109.81387992</v>
+        <v>108.81080336</v>
       </c>
       <c r="O95">
-        <v>38.434857972</v>
+        <v>38.08378117599999</v>
       </c>
       <c r="P95">
-        <v>71.379021948</v>
+        <v>70.72702218399999</v>
       </c>
       <c r="Q95">
-        <v>94.77902194800001</v>
+        <v>94.127022184</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3555217701313071</v>
+        <v>0.4052670507306029</v>
       </c>
       <c r="T95">
-        <v>5.672662989747816</v>
+        <v>6.583765273744873</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.17717276509974</v>
+        <v>2.154011352705062</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07062982304383617</v>
+        <v>0.07055202217848083</v>
       </c>
       <c r="C96">
-        <v>162.1662641931109</v>
+        <v>149.8817446600608</v>
       </c>
       <c r="D96">
-        <v>1261.787064193111</v>
+        <v>1262.735744660061</v>
       </c>
       <c r="E96">
-        <v>1240.7008</v>
+        <v>1253.934</v>
       </c>
       <c r="F96">
-        <v>1243.9208</v>
+        <v>1257.154</v>
       </c>
       <c r="G96">
         <v>144.3</v>
@@ -9159,28 +9159,28 @@
         <v>203.1</v>
       </c>
       <c r="M96">
-        <v>94.28919664000001</v>
+        <v>95.29227320000001</v>
       </c>
       <c r="N96">
-        <v>108.81080336</v>
+        <v>107.8077268</v>
       </c>
       <c r="O96">
-        <v>38.08378117599999</v>
+        <v>37.73270437999999</v>
       </c>
       <c r="P96">
-        <v>70.72702218399999</v>
+        <v>70.07502241999998</v>
       </c>
       <c r="Q96">
-        <v>94.127022184</v>
+        <v>93.47502241999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4052670507306029</v>
+        <v>0.474910443569617</v>
       </c>
       <c r="T96">
-        <v>6.583765273744873</v>
+        <v>7.859308471340753</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.154011352705062</v>
+        <v>2.131337548992377</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07055202217848083</v>
+        <v>0.0704742213131255</v>
       </c>
       <c r="C97">
-        <v>149.8817446600608</v>
+        <v>137.5986527400019</v>
       </c>
       <c r="D97">
-        <v>1262.735744660061</v>
+        <v>1263.685852740002</v>
       </c>
       <c r="E97">
-        <v>1253.934</v>
+        <v>1267.1672</v>
       </c>
       <c r="F97">
-        <v>1257.154</v>
+        <v>1270.3872</v>
       </c>
       <c r="G97">
         <v>144.3</v>
@@ -9241,28 +9241,28 @@
         <v>203.1</v>
       </c>
       <c r="M97">
-        <v>95.29227320000001</v>
+        <v>96.29534976000002</v>
       </c>
       <c r="N97">
-        <v>107.8077268</v>
+        <v>106.80465024</v>
       </c>
       <c r="O97">
-        <v>37.73270437999999</v>
+        <v>37.38162758399999</v>
       </c>
       <c r="P97">
-        <v>70.07502241999998</v>
+        <v>69.42302265599999</v>
       </c>
       <c r="Q97">
-        <v>93.47502241999999</v>
+        <v>92.82302265599998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.474910443569617</v>
+        <v>0.5793755328281381</v>
       </c>
       <c r="T97">
-        <v>7.859308471340753</v>
+        <v>9.772623267734573</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.131337548992377</v>
+        <v>2.109136116190373</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0704742213131255</v>
+        <v>0.07039642044777017</v>
       </c>
       <c r="C98">
-        <v>137.5986527400021</v>
+        <v>125.3169916578565</v>
       </c>
       <c r="D98">
-        <v>1263.685852740002</v>
+        <v>1264.637391657856</v>
       </c>
       <c r="E98">
-        <v>1267.1672</v>
+        <v>1280.4004</v>
       </c>
       <c r="F98">
-        <v>1270.3872</v>
+        <v>1283.6204</v>
       </c>
       <c r="G98">
         <v>144.3</v>
@@ -9323,28 +9323,28 @@
         <v>203.1</v>
       </c>
       <c r="M98">
-        <v>96.29534975999999</v>
+        <v>97.29842631999999</v>
       </c>
       <c r="N98">
-        <v>106.80465024</v>
+        <v>105.80157368</v>
       </c>
       <c r="O98">
-        <v>37.381627584</v>
+        <v>37.030550788</v>
       </c>
       <c r="P98">
-        <v>69.423022656</v>
+        <v>68.771022892</v>
       </c>
       <c r="Q98">
-        <v>92.82302265600001</v>
+        <v>92.171022892</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5793755328281368</v>
+        <v>0.7534840149256714</v>
       </c>
       <c r="T98">
-        <v>9.772623267734549</v>
+        <v>12.96148126172424</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.109136116190373</v>
+        <v>2.087392444889442</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07039642044777017</v>
+        <v>0.07031861958241484</v>
       </c>
       <c r="C99">
-        <v>125.3169916578565</v>
+        <v>113.0367646482659</v>
       </c>
       <c r="D99">
-        <v>1264.637391657856</v>
+        <v>1265.590364648266</v>
       </c>
       <c r="E99">
-        <v>1280.4004</v>
+        <v>1293.6336</v>
       </c>
       <c r="F99">
-        <v>1283.6204</v>
+        <v>1296.8536</v>
       </c>
       <c r="G99">
         <v>144.3</v>
@@ -9405,28 +9405,28 @@
         <v>203.1</v>
       </c>
       <c r="M99">
-        <v>97.29842631999999</v>
+        <v>98.30150288</v>
       </c>
       <c r="N99">
-        <v>105.80157368</v>
+        <v>104.79849712</v>
       </c>
       <c r="O99">
-        <v>37.030550788</v>
+        <v>36.679473992</v>
       </c>
       <c r="P99">
-        <v>68.771022892</v>
+        <v>68.11902312799999</v>
       </c>
       <c r="Q99">
-        <v>92.171022892</v>
+        <v>91.51902312799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7534840149256714</v>
+        <v>1.101700979120741</v>
       </c>
       <c r="T99">
-        <v>12.96148126172424</v>
+        <v>19.33919724970361</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.087392444889442</v>
+        <v>2.066092521982406</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07031861958241484</v>
+        <v>0.07024081871705951</v>
       </c>
       <c r="C100">
-        <v>113.0367646482659</v>
+        <v>100.7579749556312</v>
       </c>
       <c r="D100">
-        <v>1265.590364648266</v>
+        <v>1266.544774955631</v>
       </c>
       <c r="E100">
-        <v>1293.6336</v>
+        <v>1306.8668</v>
       </c>
       <c r="F100">
-        <v>1296.8536</v>
+        <v>1310.0868</v>
       </c>
       <c r="G100">
         <v>144.3</v>
@@ -9487,28 +9487,28 @@
         <v>203.1</v>
       </c>
       <c r="M100">
-        <v>98.30150288</v>
+        <v>99.30457944</v>
       </c>
       <c r="N100">
-        <v>104.79849712</v>
+        <v>103.79542056</v>
       </c>
       <c r="O100">
-        <v>36.679473992</v>
+        <v>36.328397196</v>
       </c>
       <c r="P100">
-        <v>68.11902312799999</v>
+        <v>67.467023364</v>
       </c>
       <c r="Q100">
-        <v>91.51902312799999</v>
+        <v>90.867023364</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.101700979120741</v>
+        <v>2.146351871705948</v>
       </c>
       <c r="T100">
-        <v>19.33919724970361</v>
+        <v>38.47234521364173</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.066092521982406</v>
+        <v>2.045222900548241</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07024081871705951</v>
-      </c>
-      <c r="C101">
-        <v>100.7579749556312</v>
-      </c>
-      <c r="D101">
-        <v>1266.544774955631</v>
-      </c>
-      <c r="E101">
-        <v>1306.8668</v>
-      </c>
-      <c r="F101">
-        <v>1310.0868</v>
-      </c>
-      <c r="G101">
-        <v>144.3</v>
-      </c>
-      <c r="H101">
-        <v>1320.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>226.5</v>
-      </c>
-      <c r="K101">
-        <v>23.4</v>
-      </c>
-      <c r="L101">
-        <v>203.1</v>
-      </c>
-      <c r="M101">
-        <v>99.30457944</v>
-      </c>
-      <c r="N101">
-        <v>103.79542056</v>
-      </c>
-      <c r="O101">
-        <v>36.328397196</v>
-      </c>
-      <c r="P101">
-        <v>67.467023364</v>
-      </c>
-      <c r="Q101">
-        <v>90.867023364</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.146351871705948</v>
-      </c>
-      <c r="T101">
-        <v>38.47234521364173</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.04927000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.045222900548241</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
